--- a/data/description-links.xlsx
+++ b/data/description-links.xlsx
@@ -556,7 +556,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -2320,40 +2320,40 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>רבנו בחיי אבן פקודה – חובות הלבבות</t>
+          <t>מר שושני</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>«Ховот ха-Левавот»: сущность иудейской этики</t>
+          <t>The Riddle of the Mysterious Genius: Mr. Shushani</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/eEk1_6ItRcY/edit</t>
+          <t>https://studio.youtube.com/video/unqH7pHySmM/edit</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабейну Бахья ибн Пакуда («Обязанности сердец») в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/39?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Mr. Shoshani on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/148?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/eEk1_6ItRcY</t>
+          <t>https://youtu.be/unqH7pHySmM</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>481</v>
+        <v>699</v>
       </c>
       <c r="J44" s="2" t="n"/>
     </row>
@@ -2366,36 +2366,36 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>מר שושני</t>
+          <t>רבנו בחיי אבן פקודה – חובות הלבבות</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>The Riddle of the Mysterious Genius: Mr. Shushani</t>
+          <t>«Ховот ха-Левавот»: сущность иудейской этики</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/unqH7pHySmM/edit</t>
+          <t>https://studio.youtube.com/video/eEk1_6ItRcY/edit</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>📜 Mr. Shoshani on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/148?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабейну Бахья ибн Пакуда («Обязанности сердец») в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/39?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/unqH7pHySmM</t>
+          <t>https://youtu.be/eEk1_6ItRcY</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>699</v>
+        <v>481</v>
       </c>
       <c r="J45" s="2" t="n"/>
     </row>
@@ -2618,36 +2618,36 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>הרב יוסף דוב הלוי סולובייצ׳יק (הגרי״ד)</t>
+          <t>רבי שמואל די אוזידא (בעל מדרש שמואל)</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Joseph Dov Soloveitchik - The Halakhic Man Who Lived Between Two Worlds</t>
+          <t>Рабби Шмуэль де Узеда - каббалист из Цфата, спасший мудрость ранних мудрецов от забвения</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/OXMfO24yAeU/edit</t>
+          <t>https://studio.youtube.com/video/KTKuiDElfCY/edit</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Yosef Dov HaLevi Soloveitchik (the Rav) on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/608?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Шмуэль де Узеда («Мидраш Шмуэль») в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/631?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/OXMfO24yAeU</t>
+          <t>https://youtu.be/KTKuiDElfCY</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J51" s="2" t="n"/>
     </row>
@@ -2656,40 +2656,40 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>רבי שמואל די אוזידא (בעל מדרש שמואל)</t>
+          <t>הרב יוסף דוב הלוי סולובייצ׳יק (הגרי״ד)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Рабби Шмуэль де Узеда - каббалист из Цфата, спасший мудрость ранних мудрецов от забвения</t>
+          <t>Rabbi Joseph Dov Soloveitchik - The Halakhic Man Who Lived Between Two Worlds</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/KTKuiDElfCY/edit</t>
+          <t>https://studio.youtube.com/video/OXMfO24yAeU/edit</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Шмуэль де Узеда («Мидраш Шмуэль») в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/631?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Yosef Dov HaLevi Soloveitchik (the Rav) on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/608?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/KTKuiDElfCY</t>
+          <t>https://youtu.be/OXMfO24yAeU</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J52" s="2" t="n"/>
     </row>
@@ -3202,7 +3202,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
@@ -3211,31 +3211,31 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>רבי אלכסנדרי זוסלין הכהן (המהרא״ך)</t>
+          <t>עמנואל לוינס</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>Рабби Александри Зусслин ха-Коэн — законоучитель, сохранивший Тору из пепла</t>
+          <t>Эммануэль Левинас: этика, феноменология и лицо Другого</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/D03fiiP5cJM/edit</t>
+          <t>https://studio.youtube.com/video/vyuGrknqd9g/edit</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Александри Зуслин ха-Коэн (Махарах) в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/319?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Эммануэль Левинас в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/151?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/D03fiiP5cJM</t>
+          <t>https://youtu.be/vyuGrknqd9g</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>213</v>
+        <v>384</v>
       </c>
       <c r="J65" s="2" t="n"/>
     </row>
@@ -3253,31 +3253,31 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>עמנואל לוינס</t>
+          <t>רבי אלכסנדרי זוסלין הכהן (המהרא״ך)</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>Эммануэль Левинас: этика, феноменология и лицо Другого</t>
+          <t>Рабби Александри Зусслин ха-Коэн — законоучитель, сохранивший Тору из пепла</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/vyuGrknqd9g/edit</t>
+          <t>https://studio.youtube.com/video/D03fiiP5cJM/edit</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>📜 Эммануэль Левинас в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/151?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Александри Зуслин ха-Коэн (Махарах) в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/319?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/vyuGrknqd9g</t>
+          <t>https://youtu.be/D03fiiP5cJM</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>384</v>
+        <v>213</v>
       </c>
       <c r="J66" s="2" t="n"/>
     </row>
@@ -3505,31 +3505,31 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>הרב מאיר כהנא</t>
+          <t>עמנואל לוינס</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Meir Kahane – The Ideology, Activism, and Legacy That Continue to Shake Israel</t>
+          <t>Emmanuel Levinas: Ethics, Phenomenology, and the Face of the Other</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/x_YuhpmskCM/edit</t>
+          <t>https://studio.youtube.com/video/e9KpVSP9s9E/edit</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Meir Kahane on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/197?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Emmanuel Levinas on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/151?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/x_YuhpmskCM</t>
+          <t>https://youtu.be/e9KpVSP9s9E</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>564</v>
+        <v>385</v>
       </c>
       <c r="J72" s="2" t="n"/>
     </row>
@@ -3547,31 +3547,31 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>הרב בן־ציון מאיר חי עוזיאל</t>
+          <t>הרב מאיר כהנא</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Ben-Zion Meir Hai Uziel: Thought, Halakha, and Zionism</t>
+          <t>Rabbi Meir Kahane – The Ideology, Activism, and Legacy That Continue to Shake Israel</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/L2hQKYIBlmE/edit</t>
+          <t>https://studio.youtube.com/video/x_YuhpmskCM/edit</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Ben-Zion Meir Chai Uziel on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/138?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Meir Kahane on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/197?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/L2hQKYIBlmE</t>
+          <t>https://youtu.be/x_YuhpmskCM</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>624</v>
+        <v>564</v>
       </c>
       <c r="J73" s="2" t="n"/>
     </row>
@@ -3580,7 +3580,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
@@ -3589,31 +3589,31 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>עמנואל לוינס</t>
+          <t>הרב בן־ציון מאיר חי עוזיאל</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Emmanuel Levinas: Ethics, Phenomenology, and the Face of the Other</t>
+          <t>Rabbi Ben-Zion Meir Hai Uziel: Thought, Halakha, and Zionism</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/e9KpVSP9s9E/edit</t>
+          <t>https://studio.youtube.com/video/L2hQKYIBlmE/edit</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>📜 Emmanuel Levinas on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/151?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Ben-Zion Meir Chai Uziel on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/138?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/e9KpVSP9s9E</t>
+          <t>https://youtu.be/L2hQKYIBlmE</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>385</v>
+        <v>624</v>
       </c>
       <c r="J74" s="2" t="n"/>
     </row>
@@ -4462,40 +4462,40 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>המהרש״א</t>
+          <t>חכם ציון חביב ברכה</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>Маарша — человек, соединивший разум, сердце и общественную ответственность</t>
+          <t>Rabbi Zion Haviv Bracha – the hidden kabbalist who bridged the generations of the Rashash tradition</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/oKZzcHz2jlE/edit</t>
+          <t>https://studio.youtube.com/video/uS2JTq4xVJo/edit</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>📜 Махарша в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/329?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Chacham Tzion Chaviv Bracha on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/180?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/oKZzcHz2jlE</t>
+          <t>https://youtu.be/uS2JTq4xVJo</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>329</v>
+        <v>560</v>
       </c>
       <c r="J95" s="2" t="n"/>
     </row>
@@ -4513,31 +4513,31 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>רבי יצחק מווינה (בעל האור זרוע)</t>
+          <t>המהרש״א</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Рабби Ицхак из Вены, автор «Ор Зару́а» — человек, посеявший свет между Талмудами</t>
+          <t>Маарша — человек, соединивший разум, сердце и общественную ответственность</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/ARiH1Rj5xY8/edit</t>
+          <t>https://studio.youtube.com/video/oKZzcHz2jlE/edit</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Ицхак из Вены (Ор Заруа) в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/43?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Махарша в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/329?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/ARiH1Rj5xY8</t>
+          <t>https://youtu.be/oKZzcHz2jlE</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>394</v>
+        <v>329</v>
       </c>
       <c r="J96" s="2" t="n"/>
     </row>
@@ -4550,36 +4550,36 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>חכם ציון חביב ברכה</t>
+          <t>רבי יצחק מווינה (בעל האור זרוע)</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Zion Haviv Bracha – the hidden kabbalist who bridged the generations of the Rashash tradition</t>
+          <t>Рабби Ицхак из Вены, автор «Ор Зару́а» — человек, посеявший свет между Талмудами</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/uS2JTq4xVJo/edit</t>
+          <t>https://studio.youtube.com/video/ARiH1Rj5xY8/edit</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>📜 Chacham Tzion Chaviv Bracha on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/180?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Ицхак из Вены (Ор Заруа) в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/43?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/uS2JTq4xVJo</t>
+          <t>https://youtu.be/ARiH1Rj5xY8</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>560</v>
+        <v>394</v>
       </c>
       <c r="J97" s="2" t="n"/>
     </row>
@@ -6058,40 +6058,40 @@
         <v>132</v>
       </c>
       <c r="B133" s="3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>רבי חנינא בר פפא</t>
+          <t>פרנץ רוזנצווייג – הפילוסוף שהחזיר את האדם למרכז</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>Рабби Ханина бар Папа - аморай, попросивший у Ангела смерти ещё 30 дней</t>
+          <t>Franz Rosenzweig and His Thought: Jewish Theology and Philosophy</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/oZif-VqdVNU/edit</t>
+          <t>https://studio.youtube.com/video/-KEL3MtX4nU/edit</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Ханина бар Папа в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/543?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Franz Rosenzweig on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/141?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/oZif-VqdVNU</t>
+          <t>https://youtu.be/-KEL3MtX4nU</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>47</v>
+        <v>478</v>
       </c>
       <c r="J133" s="2" t="n"/>
     </row>
@@ -6104,36 +6104,36 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>רבי דוד הלוי סגל (הט"ז)</t>
+          <t>רבי חנינא בר פפא</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>Rabbi David HaLevi Segal – The Taz: A Halakhic Authority Who Turned Law into Living Reality</t>
+          <t>Рабби Ханина бар Папа - аморай, попросивший у Ангела смерти ещё 30 дней</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/EfMLCZVUz68/edit</t>
+          <t>https://studio.youtube.com/video/oZif-VqdVNU/edit</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi David HaLevi Segal (the Taz) on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/79?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Ханина бар Папа в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/543?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/EfMLCZVUz68</t>
+          <t>https://youtu.be/oZif-VqdVNU</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>428</v>
+        <v>47</v>
       </c>
       <c r="J134" s="2" t="n"/>
     </row>
@@ -6142,40 +6142,40 @@
         <v>134</v>
       </c>
       <c r="B135" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>רב האי גאון</t>
+          <t>רבי דוד הלוי סגל (הט"ז)</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>Рабби Хай Гаон – последний из Гаонов и первый из Великих:человек, восстановивший твёрдость Галахи</t>
+          <t>Rabbi David HaLevi Segal – The Taz: A Halakhic Authority Who Turned Law into Living Reality</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/95zK1eE05_w/edit</t>
+          <t>https://studio.youtube.com/video/EfMLCZVUz68/edit</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>📜 Рав Хай Гаон в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/25?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi David HaLevi Segal (the Taz) on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/79?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/95zK1eE05_w</t>
+          <t>https://youtu.be/EfMLCZVUz68</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>584</v>
+        <v>428</v>
       </c>
       <c r="J135" s="2" t="n"/>
     </row>
@@ -6184,40 +6184,40 @@
         <v>135</v>
       </c>
       <c r="B136" s="3" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>שלמה מולכו</t>
+          <t>רב האי גאון</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>Shlomo Molcho: The Messianic Kabbalist and His Self-Sacrifice for the Sanctification of God’s Name</t>
+          <t>Рабби Хай Гаон – последний из Гаонов и первый из Великих:человек, восстановивший твёрдость Галахи</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/s7NQCbMVv90/edit</t>
+          <t>https://studio.youtube.com/video/95zK1eE05_w/edit</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>📜 Shlomo Molcho on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/326?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рав Хай Гаон в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/25?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/s7NQCbMVv90</t>
+          <t>https://youtu.be/95zK1eE05_w</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>334</v>
+        <v>584</v>
       </c>
       <c r="J136" s="2" t="n"/>
     </row>
@@ -6230,36 +6230,36 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>הרב שמואל מוהליבר – מנהיג דתי ומבשר הציונות</t>
+          <t>שלמה מולכו</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>Раввин Шмуэль Моаливер: пионер религиозного сионизма</t>
+          <t>Shlomo Molcho: The Messianic Kabbalist and His Self-Sacrifice for the Sanctification of God’s Name</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/vUjK21VU1Ww/edit</t>
+          <t>https://studio.youtube.com/video/s7NQCbMVv90/edit</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>📜 Рав Шмуэль Мохливер в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/120?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Shlomo Molcho on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/326?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/vUjK21VU1Ww</t>
+          <t>https://youtu.be/s7NQCbMVv90</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>472</v>
+        <v>334</v>
       </c>
       <c r="J137" s="2" t="n"/>
     </row>
@@ -6272,36 +6272,36 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>פרנץ רוזנצווייג – הפילוסוף שהחזיר את האדם למרכז</t>
+          <t>הרב שמואל מוהליבר – מנהיג דתי ומבשר הציונות</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>Franz Rosenzweig and His Thought: Jewish Theology and Philosophy</t>
+          <t>Раввин Шмуэль Моаливер: пионер религиозного сионизма</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/-KEL3MtX4nU/edit</t>
+          <t>https://studio.youtube.com/video/vUjK21VU1Ww/edit</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>📜 Franz Rosenzweig on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/141?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рав Шмуэль Мохливер в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/120?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/-KEL3MtX4nU</t>
+          <t>https://youtu.be/vUjK21VU1Ww</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="J138" s="2" t="n"/>
     </row>
@@ -6352,7 +6352,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
@@ -8162,36 +8162,36 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>תודוס איש רומי</t>
+          <t>רבי אלעזר מגרמייזא (בעל הרוקח)</t>
         </is>
       </c>
       <c r="E183" s="7" t="inlineStr">
         <is>
-          <t>Религиозная власть и имперская политика в Древнем Риме</t>
+          <t>Rabbi Eleazar of Worms and the Ordinances of ShUM</t>
         </is>
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/LJjUME0eG6g/edit</t>
+          <t>https://studio.youtube.com/video/XewrhViUp7E/edit</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>📜 Теодос из Рима в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/485?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Elazar of Worms (the Rokeach) on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/280?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/LJjUME0eG6g</t>
+          <t>https://youtu.be/XewrhViUp7E</t>
         </is>
       </c>
       <c r="I183" s="2" t="n">
-        <v>458</v>
+        <v>264</v>
       </c>
       <c r="J183" s="2" t="n"/>
     </row>
@@ -8204,36 +8204,36 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>עברית</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>הרב יצחק יעקב ריינס</t>
-        </is>
-      </c>
-      <c r="E184" s="5" t="inlineStr">
-        <is>
-          <t>הרב יצחק יעקב ריינס ומייסד המזרחי</t>
+          <t>תודוס איש רומי</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>Религиозная власть и имперская политика в Древнем Риме</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/BVYplCpF02c/edit</t>
-        </is>
-      </c>
-      <c r="G184" s="5" t="inlineStr">
-        <is>
-          <t>📜 הרב יצחק יעקב ריינס באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/489?utm_source=youtube&amp;utm_medium=video</t>
+          <t>https://studio.youtube.com/video/LJjUME0eG6g/edit</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>📜 Теодос из Рима в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/485?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/BVYplCpF02c</t>
+          <t>https://youtu.be/LJjUME0eG6g</t>
         </is>
       </c>
       <c r="I184" s="2" t="n">
-        <v>686</v>
+        <v>458</v>
       </c>
       <c r="J184" s="2" t="n"/>
     </row>
@@ -8242,40 +8242,40 @@
         <v>184</v>
       </c>
       <c r="B185" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>עברית</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>רבי אלעזר מגרמייזא (בעל הרוקח)</t>
-        </is>
-      </c>
-      <c r="E185" s="7" t="inlineStr">
-        <is>
-          <t>Rabbi Eleazar of Worms and the Ordinances of ShUM</t>
+          <t>הרב יצחק יעקב ריינס</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>הרב יצחק יעקב ריינס ומייסד המזרחי</t>
         </is>
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/XewrhViUp7E/edit</t>
-        </is>
-      </c>
-      <c r="G185" s="7" t="inlineStr">
-        <is>
-          <t>📜 Rabbi Elazar of Worms (the Rokeach) on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/280?utm_source=youtube&amp;utm_medium=video</t>
+          <t>https://studio.youtube.com/video/BVYplCpF02c/edit</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>📜 הרב יצחק יעקב ריינס באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/489?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/XewrhViUp7E</t>
+          <t>https://youtu.be/BVYplCpF02c</t>
         </is>
       </c>
       <c r="I185" s="2" t="n">
-        <v>264</v>
+        <v>686</v>
       </c>
       <c r="J185" s="2" t="n"/>
     </row>
@@ -8293,31 +8293,31 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>רבנו בחיי אבן פקודה – חובות הלבבות</t>
+          <t>ילקוט שמעוני</t>
         </is>
       </c>
       <c r="E186" s="7" t="inlineStr">
         <is>
-          <t>“Duties of the Heart”: The Essence of Jewish Ethics</t>
+          <t>Yalkut Shimoni – the book that introduced nothing new, yet saved an entire world</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/k5g7dfUeBlw/edit</t>
+          <t>https://studio.youtube.com/video/nAV7hB3__Lk/edit</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbenu Bachya ibn Paquda (Duties of the Heart) on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/39?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Yalkut Shimoni on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/55?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H186" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/k5g7dfUeBlw</t>
+          <t>https://youtu.be/nAV7hB3__Lk</t>
         </is>
       </c>
       <c r="I186" s="2" t="n">
-        <v>480</v>
+        <v>402</v>
       </c>
       <c r="J186" s="2" t="n"/>
     </row>
@@ -8326,7 +8326,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
@@ -8335,31 +8335,31 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>ילקוט שמעוני</t>
+          <t>רבנו בחיי אבן פקודה – חובות הלבבות</t>
         </is>
       </c>
       <c r="E187" s="7" t="inlineStr">
         <is>
-          <t>Yalkut Shimoni – the book that introduced nothing new, yet saved an entire world</t>
+          <t>“Duties of the Heart”: The Essence of Jewish Ethics</t>
         </is>
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/nAV7hB3__Lk/edit</t>
+          <t>https://studio.youtube.com/video/k5g7dfUeBlw/edit</t>
         </is>
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>📜 Yalkut Shimoni on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/55?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbenu Bachya ibn Paquda (Duties of the Heart) on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/39?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/nAV7hB3__Lk</t>
+          <t>https://youtu.be/k5g7dfUeBlw</t>
         </is>
       </c>
       <c r="I187" s="2" t="n">
-        <v>402</v>
+        <v>480</v>
       </c>
       <c r="J187" s="2" t="n"/>
     </row>
@@ -8498,36 +8498,36 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>רפרם בר פפא</t>
+          <t>רבי אברהם בן שלמה הלוי בוקראט</t>
         </is>
       </c>
       <c r="E191" s="7" t="inlineStr">
         <is>
-          <t>Rafram bar Pappa - The Amora Who Connected Halakha, Science, and the Destruction of the Temple</t>
+          <t>Рабби Авраам Бократ - мудрец, изгнанный из Испании и выступивший в защиту РашиРабби Ав</t>
         </is>
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/F970V-O0D_M/edit</t>
+          <t>https://studio.youtube.com/video/llK6TjhR-ok/edit</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>📜 Rafram bar Pappa on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/552?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Авраам бен Шломо а-Леви Букрат в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/627?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H191" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/F970V-O0D_M</t>
+          <t>https://youtu.be/llK6TjhR-ok</t>
         </is>
       </c>
       <c r="I191" s="2" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="J191" s="2" t="n"/>
     </row>
@@ -8540,36 +8540,36 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>הצמח צדק (רבי מנחם מנדל שניאורסון)</t>
+          <t>רפרם בר פפא</t>
         </is>
       </c>
       <c r="E192" s="7" t="inlineStr">
         <is>
-          <t>Цемах Цедек - Ребе, превративший Хабад в центр Галахи и духовного руководства</t>
+          <t>Rafram bar Pappa - The Amora Who Connected Halakha, Science, and the Destruction of the Temple</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/27qzVovmga0/edit</t>
+          <t>https://studio.youtube.com/video/F970V-O0D_M/edit</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>📜 Цемах Цедек в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/501?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rafram bar Pappa on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/552?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H192" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/27qzVovmga0</t>
+          <t>https://youtu.be/F970V-O0D_M</t>
         </is>
       </c>
       <c r="I192" s="2" t="n">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="J192" s="2" t="n"/>
     </row>
@@ -8582,36 +8582,36 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>רבנו תם (ר׳ יעקב בן מאיר) – מהפכן השיטה התוספתית</t>
+          <t>הצמח צדק (רבי מנחם מנדל שניאורסון)</t>
         </is>
       </c>
       <c r="E193" s="7" t="inlineStr">
         <is>
-          <t>Rabbeinu Tam: Architect of Talmudic Scholarship and the Tosafists’ Legacy</t>
+          <t>Цемах Цедек - Ребе, превративший Хабад в центр Галахи и духовного руководства</t>
         </is>
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/s0OXFxwzbvY/edit</t>
+          <t>https://studio.youtube.com/video/27qzVovmga0/edit</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbenu Tam (R. Yaakov ben Meir) on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/33?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Цемах Цедек в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/501?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H193" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/s0OXFxwzbvY</t>
+          <t>https://youtu.be/27qzVovmga0</t>
         </is>
       </c>
       <c r="I193" s="2" t="n">
-        <v>462</v>
+        <v>142</v>
       </c>
       <c r="J193" s="2" t="n"/>
     </row>
@@ -8620,40 +8620,40 @@
         <v>193</v>
       </c>
       <c r="B194" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>רבי אברהם בן שלמה הלוי בוקראט</t>
+          <t>רבנו תם (ר׳ יעקב בן מאיר) – מהפכן השיטה התוספתית</t>
         </is>
       </c>
       <c r="E194" s="7" t="inlineStr">
         <is>
-          <t>Рабби Авраам Бократ - мудрец, изгнанный из Испании и выступивший в защиту РашиРабби Ав</t>
+          <t>Rabbeinu Tam: Architect of Talmudic Scholarship and the Tosafists’ Legacy</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/llK6TjhR-ok/edit</t>
+          <t>https://studio.youtube.com/video/s0OXFxwzbvY/edit</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Авраам бен Шломо а-Леви Букрат в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/627?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbenu Tam (R. Yaakov ben Meir) on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/33?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H194" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/llK6TjhR-ok</t>
+          <t>https://youtu.be/s0OXFxwzbvY</t>
         </is>
       </c>
       <c r="I194" s="2" t="n">
-        <v>7</v>
+        <v>462</v>
       </c>
       <c r="J194" s="2" t="n"/>
     </row>
@@ -8662,40 +8662,40 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>רבי יעקב פולק</t>
+          <t>הרב מרדכי שרעבי</t>
         </is>
       </c>
       <c r="E195" s="7" t="inlineStr">
         <is>
-          <t>Рабби Яаков Поллак: основатель метода пилпула и зарождения мира Торы в Польше</t>
+          <t>Biography of Rabbi Mordechai Sharabi, Kabbalist</t>
         </is>
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/L5T6oVKBsSU/edit</t>
+          <t>https://studio.youtube.com/video/UP9MKbxXoUw/edit</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Яаков Поллак в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/457?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Mordechai Sharabi on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/154?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H195" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/L5T6oVKBsSU</t>
+          <t>https://youtu.be/UP9MKbxXoUw</t>
         </is>
       </c>
       <c r="I195" s="2" t="n">
-        <v>169</v>
+        <v>616</v>
       </c>
       <c r="J195" s="2" t="n"/>
     </row>
@@ -8713,31 +8713,31 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>הר"ן (רבנו נסים מגירונה)</t>
+          <t>רבי יעקב פולק</t>
         </is>
       </c>
       <c r="E196" s="7" t="inlineStr">
         <is>
-          <t>Рабби Ниссим из Гироны (Ран): лидерство, галаха и философия в испанском иудаизме</t>
+          <t>Рабби Яаков Поллак: основатель метода пилпула и зарождения мира Торы в Польше</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/h0NH3WSv5YA/edit</t>
+          <t>https://studio.youtube.com/video/L5T6oVKBsSU/edit</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>📜 Ран (рабейну Ниссим из Жироны) в «Оцар Хахамим» — полное исследование и его ученики: https://ozar-chachamim-app.vercel.app/ru/sage/13?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Яаков Поллак в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/457?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H196" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/h0NH3WSv5YA</t>
+          <t>https://youtu.be/L5T6oVKBsSU</t>
         </is>
       </c>
       <c r="I196" s="2" t="n">
-        <v>352</v>
+        <v>169</v>
       </c>
       <c r="J196" s="2" t="n"/>
     </row>
@@ -8750,36 +8750,36 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>הרב שלום שרעבי (הרש"ש)</t>
+          <t>הר"ן (רבנו נסים מגירונה)</t>
         </is>
       </c>
       <c r="E197" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Shalom Sharabi: The Father of Sephardic Kabbalists and the World of Kavanot</t>
+          <t>Рабби Ниссим из Гироны (Ран): лидерство, галаха и философия в испанском иудаизме</t>
         </is>
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/HvMt-duFwZA/edit</t>
+          <t>https://studio.youtube.com/video/h0NH3WSv5YA/edit</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Shalom Sharabi (the Rashash) on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/96?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Ран (рабейну Ниссим из Жироны) в «Оцар Хахамим» — полное исследование и его ученики: https://ozar-chachamim-app.vercel.app/ru/sage/13?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H197" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/HvMt-duFwZA</t>
+          <t>https://youtu.be/h0NH3WSv5YA</t>
         </is>
       </c>
       <c r="I197" s="2" t="n">
-        <v>553</v>
+        <v>352</v>
       </c>
       <c r="J197" s="2" t="n"/>
     </row>
@@ -8797,31 +8797,31 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>הרב מרדכי שרעבי</t>
+          <t>הרב שלום שרעבי (הרש"ש)</t>
         </is>
       </c>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>Biography of Rabbi Mordechai Sharabi, Kabbalist</t>
+          <t>Rabbi Shalom Sharabi: The Father of Sephardic Kabbalists and the World of Kavanot</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/UP9MKbxXoUw/edit</t>
+          <t>https://studio.youtube.com/video/HvMt-duFwZA/edit</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Mordechai Sharabi on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/154?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Shalom Sharabi (the Rashash) on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/96?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H198" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/UP9MKbxXoUw</t>
+          <t>https://youtu.be/HvMt-duFwZA</t>
         </is>
       </c>
       <c r="I198" s="2" t="n">
-        <v>616</v>
+        <v>553</v>
       </c>
       <c r="J198" s="2" t="n"/>
     </row>
@@ -10300,7 +10300,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
@@ -10309,31 +10309,31 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>הרב ד״ר אברהם לבני</t>
+          <t>הרב שמואל בורנשטיין – בעל 'שם משמואל'</t>
         </is>
       </c>
       <c r="E234" s="7" t="inlineStr">
         <is>
-          <t>Abraham Livni: The Israeli Secret and the Message to the World</t>
+          <t>Rabbi Shmuel Bornsztain - The Rebbe Whose Embrace Defied Death</t>
         </is>
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/7xG6akhghaE/edit</t>
+          <t>https://studio.youtube.com/video/p4s-C-bZxak/edit</t>
         </is>
       </c>
       <c r="G234" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Dr. Avraham Livni on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/456?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Shmuel Bornsztain (the Shem MiShmuel) on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/131?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H234" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/7xG6akhghaE</t>
+          <t>https://youtu.be/p4s-C-bZxak</t>
         </is>
       </c>
       <c r="I234" s="2" t="n">
-        <v>172</v>
+        <v>665</v>
       </c>
       <c r="J234" s="2" t="n"/>
     </row>
@@ -10346,36 +10346,36 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>גירוש ספרד</t>
+          <t>הרב ד״ר אברהם לבני</t>
         </is>
       </c>
       <c r="E235" s="7" t="inlineStr">
         <is>
-          <t>Наследие сефардского еврейства: от изгнания к рассеянию и до наших дней</t>
+          <t>Abraham Livni: The Israeli Secret and the Message to the World</t>
         </is>
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/AKaU3ACKg08/edit</t>
+          <t>https://studio.youtube.com/video/7xG6akhghaE/edit</t>
         </is>
       </c>
       <c r="G235" s="7" t="inlineStr">
         <is>
-          <t>📜 Изгнание из Испании в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/331?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Dr. Avraham Livni on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/456?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H235" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/AKaU3ACKg08</t>
+          <t>https://youtu.be/7xG6akhghaE</t>
         </is>
       </c>
       <c r="I235" s="2" t="n">
-        <v>308</v>
+        <v>172</v>
       </c>
       <c r="J235" s="2" t="n"/>
     </row>
@@ -10393,31 +10393,31 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>יעקב בן אשר</t>
+          <t>גירוש ספרד</t>
         </is>
       </c>
       <c r="E236" s="7" t="inlineStr">
         <is>
-          <t>«Арбаа Турим» и Бааль ха-Турим: архитектура галахи и толкование Торы</t>
+          <t>Наследие сефардского еврейства: от изгнания к рассеянию и до наших дней</t>
         </is>
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/kkcdpEijKKU/edit</t>
+          <t>https://studio.youtube.com/video/AKaU3ACKg08/edit</t>
         </is>
       </c>
       <c r="G236" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Яаков бен Ашер (Тур) в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/189?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Изгнание из Испании в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/331?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H236" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/kkcdpEijKKU</t>
+          <t>https://youtu.be/AKaU3ACKg08</t>
         </is>
       </c>
       <c r="I236" s="2" t="n">
-        <v>447</v>
+        <v>308</v>
       </c>
       <c r="J236" s="2" t="n"/>
     </row>
@@ -10430,36 +10430,36 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>הרב שמואל בורנשטיין – בעל 'שם משמואל'</t>
+          <t>יעקב בן אשר</t>
         </is>
       </c>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Shmuel Bornsztain - The Rebbe Whose Embrace Defied Death</t>
+          <t>«Арбаа Турим» и Бааль ха-Турим: архитектура галахи и толкование Торы</t>
         </is>
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/p4s-C-bZxak/edit</t>
+          <t>https://studio.youtube.com/video/kkcdpEijKKU/edit</t>
         </is>
       </c>
       <c r="G237" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Shmuel Bornsztain (the Shem MiShmuel) on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/131?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Яаков бен Ашер (Тур) в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/189?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H237" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/p4s-C-bZxak</t>
+          <t>https://youtu.be/kkcdpEijKKU</t>
         </is>
       </c>
       <c r="I237" s="2" t="n">
-        <v>665</v>
+        <v>447</v>
       </c>
       <c r="J237" s="2" t="n"/>
     </row>
@@ -10603,31 +10603,31 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>רבי אפרים אנקווה – 'הרב הרוכב על האריה'</t>
+          <t>הרב יהודה אלקלעי – תשובה שהופכת לתוכנית לאומית</t>
         </is>
       </c>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Ephraim Ankawa: His Life and Legacy</t>
+          <t>Alkalai: The Harbinger of Political Zionism</t>
         </is>
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/v9NtNryySZ0/edit</t>
+          <t>https://studio.youtube.com/video/dQ69FzKEc94/edit</t>
         </is>
       </c>
       <c r="G241" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Ephraim Ankawa on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/58?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Yehuda Alkalai on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/108?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H241" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/v9NtNryySZ0</t>
+          <t>https://youtu.be/dQ69FzKEc94</t>
         </is>
       </c>
       <c r="I241" s="2" t="n">
-        <v>671</v>
+        <v>486</v>
       </c>
       <c r="J241" s="2" t="n"/>
     </row>
@@ -10636,40 +10636,40 @@
         <v>241</v>
       </c>
       <c r="B242" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>רבי יוסף ג'יקטיליה</t>
+          <t>רבי אפרים אנקווה – 'הרב הרוכב על האריה'</t>
         </is>
       </c>
       <c r="E242" s="7" t="inlineStr">
         <is>
-          <t>Рабби Йосеф Джикатилья: «Врата света» и тайны Божественного Имени</t>
+          <t>Rabbi Ephraim Ankawa: His Life and Legacy</t>
         </is>
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/FCgf1OySW6Y/edit</t>
+          <t>https://studio.youtube.com/video/v9NtNryySZ0/edit</t>
         </is>
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Йосеф Гикатилла в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/471?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Ephraim Ankawa on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/58?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H242" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/FCgf1OySW6Y</t>
+          <t>https://youtu.be/v9NtNryySZ0</t>
         </is>
       </c>
       <c r="I242" s="2" t="n">
-        <v>151</v>
+        <v>671</v>
       </c>
       <c r="J242" s="2" t="n"/>
     </row>
@@ -10682,36 +10682,36 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>רבי מאיר בן ברוך הלוי (מהר״ם סג״ל)</t>
+          <t>רבי יוסף ג'יקטיליה</t>
         </is>
       </c>
       <c r="E243" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Meir ben Baruch HaLevi Segal – The Man Who Reshaped Ashkenazi Rabbinic Authority</t>
+          <t>Рабби Йосеф Джикатилья: «Врата света» и тайны Божественного Имени</t>
         </is>
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/FBL394gsb4g/edit</t>
+          <t>https://studio.youtube.com/video/FCgf1OySW6Y/edit</t>
         </is>
       </c>
       <c r="G243" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Meir ben Baruch HaLevi (Maharam Segal) on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/425?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Йосеф Гикатилла в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/471?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H243" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/FBL394gsb4g</t>
+          <t>https://youtu.be/FCgf1OySW6Y</t>
         </is>
       </c>
       <c r="I243" s="2" t="n">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="J243" s="2" t="n"/>
     </row>
@@ -10724,36 +10724,36 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>חולדה הנביאה</t>
+          <t>רבי מאיר בן ברוך הלוי (מהר״ם סג״ל)</t>
         </is>
       </c>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>Пророчица Хульда — история открытия книги Торы в Храме</t>
+          <t>Rabbi Meir ben Baruch HaLevi Segal – The Man Who Reshaped Ashkenazi Rabbinic Authority</t>
         </is>
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/FQ0SYVbT4y4/edit</t>
+          <t>https://studio.youtube.com/video/FBL394gsb4g/edit</t>
         </is>
       </c>
       <c r="G244" s="7" t="inlineStr">
         <is>
-          <t>📜 Пророчица Хульда в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/270?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Meir ben Baruch HaLevi (Maharam Segal) on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/425?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H244" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/FQ0SYVbT4y4</t>
+          <t>https://youtu.be/FBL394gsb4g</t>
         </is>
       </c>
       <c r="I244" s="2" t="n">
-        <v>273</v>
+        <v>202</v>
       </c>
       <c r="J244" s="2" t="n"/>
     </row>
@@ -10766,36 +10766,36 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>רבי שלמה הלוי אלקבץ</t>
+          <t>חולדה הנביאה</t>
         </is>
       </c>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Shlomo Alkabetz: Architect of Kabbalah, Shabbat, and Liturgical Poetry in Safed</t>
+          <t>Пророчица Хульда — история открытия книги Торы в Храме</t>
         </is>
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/0Grw9xmokQs/edit</t>
+          <t>https://studio.youtube.com/video/FQ0SYVbT4y4/edit</t>
         </is>
       </c>
       <c r="G245" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Shlomo HaLevi Alkabetz on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/327?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Пророчица Хульда в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/270?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H245" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/0Grw9xmokQs</t>
+          <t>https://youtu.be/FQ0SYVbT4y4</t>
         </is>
       </c>
       <c r="I245" s="2" t="n">
-        <v>336</v>
+        <v>273</v>
       </c>
       <c r="J245" s="2" t="n"/>
     </row>
@@ -10808,36 +10808,36 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>הרב אברהם יהושע השל – הגות ומעורבות מוסרית</t>
+          <t>רבי שלמה הלוי אלקבץ</t>
         </is>
       </c>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>Раввин Авраам Джошуа Хешель — философия, нравственная ответственность и человеческая вовлечённость</t>
+          <t>Rabbi Shlomo Alkabetz: Architect of Kabbalah, Shabbat, and Liturgical Poetry in Safed</t>
         </is>
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/ASOGLLfZ_DE/edit</t>
+          <t>https://studio.youtube.com/video/0Grw9xmokQs/edit</t>
         </is>
       </c>
       <c r="G246" s="7" t="inlineStr">
         <is>
-          <t>📜 Рав Авраам Йехошуа Хешель в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/152?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Shlomo HaLevi Alkabetz on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/327?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H246" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/ASOGLLfZ_DE</t>
+          <t>https://youtu.be/0Grw9xmokQs</t>
         </is>
       </c>
       <c r="I246" s="2" t="n">
-        <v>468</v>
+        <v>336</v>
       </c>
       <c r="J246" s="2" t="n"/>
     </row>
@@ -10850,36 +10850,36 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>הרב יהודה אלקלעי – תשובה שהופכת לתוכנית לאומית</t>
+          <t>הרב אברהם יהושע השל – הגות ומעורבות מוסרית</t>
         </is>
       </c>
       <c r="E247" s="7" t="inlineStr">
         <is>
-          <t>Alkalai: The Harbinger of Political Zionism</t>
+          <t>Раввин Авраам Джошуа Хешель — философия, нравственная ответственность и человеческая вовлечённость</t>
         </is>
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/dQ69FzKEc94/edit</t>
+          <t>https://studio.youtube.com/video/ASOGLLfZ_DE/edit</t>
         </is>
       </c>
       <c r="G247" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Yehuda Alkalai on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/108?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рав Авраам Йехошуа Хешель в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/152?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H247" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/dQ69FzKEc94</t>
+          <t>https://youtu.be/ASOGLLfZ_DE</t>
         </is>
       </c>
       <c r="I247" s="2" t="n">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="J247" s="2" t="n"/>
     </row>
@@ -14336,36 +14336,36 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>רבי חיים מוולוז'ין – מייסד 'אם הישיבות' ו'נפש החיים'</t>
+          <t>רבי יוסף אלבו</t>
         </is>
       </c>
       <c r="E330" s="7" t="inlineStr">
         <is>
-          <t>Рабби Хаим из Воложина — тихий революционер, сформировавший позвоночник мира Торы</t>
+          <t>Rabbi Joseph Albo – The Sage Who Preserved Faith in a Time of Crisis</t>
         </is>
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/D5ctLfiF46Q/edit</t>
+          <t>https://studio.youtube.com/video/gmQs0iEFQo0/edit</t>
         </is>
       </c>
       <c r="G330" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Хаим из Воложина в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/99?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Yosef Albo on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/17?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H330" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/D5ctLfiF46Q</t>
+          <t>https://youtu.be/gmQs0iEFQo0</t>
         </is>
       </c>
       <c r="I330" s="2" t="n">
-        <v>657</v>
+        <v>594</v>
       </c>
       <c r="J330" s="2" t="n"/>
     </row>
@@ -14374,40 +14374,40 @@
         <v>330</v>
       </c>
       <c r="B331" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>צרויה</t>
+          <t>רבי חיים מוולוז'ין – מייסד 'אם הישיבות' ו'נפש החיים'</t>
         </is>
       </c>
       <c r="E331" s="7" t="inlineStr">
         <is>
-          <t>Zeruiah - The Woman Whose Sons Bore Her Name at the Heart of David’s Kingdom</t>
+          <t>Рабби Хаим из Воложина — тихий революционер, сформировавший позвоночник мира Торы</t>
         </is>
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/VbKKhrAATyE/edit</t>
+          <t>https://studio.youtube.com/video/D5ctLfiF46Q/edit</t>
         </is>
       </c>
       <c r="G331" s="7" t="inlineStr">
         <is>
-          <t>📜 Zeruiah on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/535?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Хаим из Воложина в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/99?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H331" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/VbKKhrAATyE</t>
+          <t>https://youtu.be/D5ctLfiF46Q</t>
         </is>
       </c>
       <c r="I331" s="2" t="n">
-        <v>50</v>
+        <v>657</v>
       </c>
       <c r="J331" s="2" t="n"/>
     </row>
@@ -14425,31 +14425,31 @@
       </c>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>דונה גרציה נשיא</t>
+          <t>צרויה</t>
         </is>
       </c>
       <c r="E332" s="7" t="inlineStr">
         <is>
-          <t>Dona Gracia Nasi - The Woman Who Turned Wealth and Political Power into a Jewish Rescue Mission</t>
+          <t>Zeruiah - The Woman Whose Sons Bore Her Name at the Heart of David’s Kingdom</t>
         </is>
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/xQ2dUpSvXYU/edit</t>
+          <t>https://studio.youtube.com/video/VbKKhrAATyE/edit</t>
         </is>
       </c>
       <c r="G332" s="7" t="inlineStr">
         <is>
-          <t>📜 Doña Gracia Nasi on Ozar Chachamim — the full research and a quiz: https://ozar-chachamim-app.vercel.app/en/sage/524?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Zeruiah on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/535?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H332" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/xQ2dUpSvXYU</t>
+          <t>https://youtu.be/VbKKhrAATyE</t>
         </is>
       </c>
       <c r="I332" s="2" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J332" s="2" t="n"/>
     </row>
@@ -14467,31 +14467,31 @@
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>רבי גדליה נדל</t>
+          <t>דונה גרציה נשיא</t>
         </is>
       </c>
       <c r="E333" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Gedaliah Nadel - Torah, Science, and the Search for Truth</t>
+          <t>Dona Gracia Nasi - The Woman Who Turned Wealth and Political Power into a Jewish Rescue Mission</t>
         </is>
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/b3MGed9-cb0/edit</t>
+          <t>https://studio.youtube.com/video/xQ2dUpSvXYU/edit</t>
         </is>
       </c>
       <c r="G333" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Gedalia Nadel on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/541?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Doña Gracia Nasi on Ozar Chachamim — the full research and a quiz: https://ozar-chachamim-app.vercel.app/en/sage/524?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H333" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/b3MGed9-cb0</t>
+          <t>https://youtu.be/xQ2dUpSvXYU</t>
         </is>
       </c>
       <c r="I333" s="2" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="J333" s="2" t="n"/>
     </row>
@@ -14504,7 +14504,7 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -14514,26 +14514,26 @@
       </c>
       <c r="E334" s="7" t="inlineStr">
         <is>
-          <t>Раввин Гедалия Надель - Тора, наука и поиск истины</t>
+          <t>Rabbi Gedaliah Nadel - Torah, Science, and the Search for Truth</t>
         </is>
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/VC4hexRfopM/edit</t>
+          <t>https://studio.youtube.com/video/b3MGed9-cb0/edit</t>
         </is>
       </c>
       <c r="G334" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Гедалья Надель в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/541?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Gedalia Nadel on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/541?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H334" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/VC4hexRfopM</t>
+          <t>https://youtu.be/b3MGed9-cb0</t>
         </is>
       </c>
       <c r="I334" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J334" s="2" t="n"/>
     </row>
@@ -14551,31 +14551,31 @@
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>רבי יחיאל בן יקותיאל ענו</t>
+          <t>רבי גדליה נדל</t>
         </is>
       </c>
       <c r="E335" s="7" t="inlineStr">
         <is>
-          <t>Рабби Йехиэль бен Йекутиэль: Лейденская рукопись</t>
+          <t>Раввин Гедалия Надель - Тора, наука и поиск истины</t>
         </is>
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/BX0hmaRuQm0/edit</t>
+          <t>https://studio.youtube.com/video/VC4hexRfopM/edit</t>
         </is>
       </c>
       <c r="G335" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Йехиэль бен Йекутиэль Анав в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/397?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Гедалья Надель в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/541?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H335" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/BX0hmaRuQm0</t>
+          <t>https://youtu.be/VC4hexRfopM</t>
         </is>
       </c>
       <c r="I335" s="2" t="n">
-        <v>241</v>
+        <v>76</v>
       </c>
       <c r="J335" s="2" t="n"/>
     </row>
@@ -14593,31 +14593,31 @@
       </c>
       <c r="D336" s="4" t="inlineStr">
         <is>
-          <t>הרב עובדיה הדאיה</t>
+          <t>רבי יחיאל בן יקותיאל ענו</t>
         </is>
       </c>
       <c r="E336" s="7" t="inlineStr">
         <is>
-          <t>Рав Овадия Адая: опора галахического учения, каббалы и сионизма</t>
+          <t>Рабби Йехиэль бен Йекутиэль: Лейденская рукопись</t>
         </is>
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/TavL4Mjk7g0/edit</t>
+          <t>https://studio.youtube.com/video/BX0hmaRuQm0/edit</t>
         </is>
       </c>
       <c r="G336" s="7" t="inlineStr">
         <is>
-          <t>📜 Рав Овадья Хадая в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/144?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Йехиэль бен Йекутиэль Анав в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/397?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H336" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/TavL4Mjk7g0</t>
+          <t>https://youtu.be/BX0hmaRuQm0</t>
         </is>
       </c>
       <c r="I336" s="2" t="n">
-        <v>368</v>
+        <v>241</v>
       </c>
       <c r="J336" s="2" t="n"/>
     </row>
@@ -14630,36 +14630,36 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>הרב יצחק אלפייה</t>
+          <t>הרב עובדיה הדאיה</t>
         </is>
       </c>
       <c r="E337" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Yitzhak Alfiya: His Teachings and Legacy</t>
+          <t>Рав Овадия Адая: опора галахического учения, каббалы и сионизма</t>
         </is>
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/Z2ywjHTTFuE/edit</t>
+          <t>https://studio.youtube.com/video/TavL4Mjk7g0/edit</t>
         </is>
       </c>
       <c r="G337" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Yitzchak Alfiya on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/137?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рав Овадья Хадая в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/144?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H337" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/Z2ywjHTTFuE</t>
+          <t>https://youtu.be/TavL4Mjk7g0</t>
         </is>
       </c>
       <c r="I337" s="2" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J337" s="2" t="n"/>
     </row>
@@ -14677,31 +14677,31 @@
       </c>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>הראבי"ה (רבי אליעזר בן יואל הלוי)</t>
+          <t>הרב יצחק אלפייה</t>
         </is>
       </c>
       <c r="E338" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Eliezer ben Joel HaLevi (Ra’avyah): His Legacy, Halakhic Authority, and Life Story</t>
+          <t>Rabbi Yitzhak Alfiya: His Teachings and Legacy</t>
         </is>
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/RDA9SnI7ZD0/edit</t>
+          <t>https://studio.youtube.com/video/Z2ywjHTTFuE/edit</t>
         </is>
       </c>
       <c r="G338" s="7" t="inlineStr">
         <is>
-          <t>📜 The Ra'avia on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/49?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Yitzchak Alfiya on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/137?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H338" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/RDA9SnI7ZD0</t>
+          <t>https://youtu.be/Z2ywjHTTFuE</t>
         </is>
       </c>
       <c r="I338" s="2" t="n">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="J338" s="2" t="n"/>
     </row>
@@ -14714,36 +14714,36 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>הבן איש חי (רבי יוסף חיים מבגדד)</t>
+          <t>הראבי"ה (רבי אליעזר בן יואל הלוי)</t>
         </is>
       </c>
       <c r="E339" s="7" t="inlineStr">
         <is>
-          <t>Рабби Йосеф Хаим из Багдада: учение, социальная критика и наследие</t>
+          <t>Rabbi Eliezer ben Joel HaLevi (Ra’avyah): His Legacy, Halakhic Authority, and Life Story</t>
         </is>
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/ST3uDsJdluA/edit</t>
+          <t>https://studio.youtube.com/video/RDA9SnI7ZD0/edit</t>
         </is>
       </c>
       <c r="G339" s="7" t="inlineStr">
         <is>
-          <t>📜 Бен Иш Хай в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/126?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 The Ra'avia on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/49?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H339" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/ST3uDsJdluA</t>
+          <t>https://youtu.be/RDA9SnI7ZD0</t>
         </is>
       </c>
       <c r="I339" s="2" t="n">
-        <v>485</v>
+        <v>397</v>
       </c>
       <c r="J339" s="2" t="n"/>
     </row>
@@ -14756,36 +14756,36 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>רבי יוסף אלבו</t>
+          <t>הבן איש חי (רבי יוסף חיים מבגדד)</t>
         </is>
       </c>
       <c r="E340" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Joseph Albo – The Sage Who Preserved Faith in a Time of Crisis</t>
+          <t>Рабби Йосеф Хаим из Багдада: учение, социальная критика и наследие</t>
         </is>
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/gmQs0iEFQo0/edit</t>
+          <t>https://studio.youtube.com/video/ST3uDsJdluA/edit</t>
         </is>
       </c>
       <c r="G340" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Yosef Albo on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/17?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Бен Иш Хай в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/126?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H340" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/gmQs0iEFQo0</t>
+          <t>https://youtu.be/ST3uDsJdluA</t>
         </is>
       </c>
       <c r="I340" s="2" t="n">
-        <v>594</v>
+        <v>485</v>
       </c>
       <c r="J340" s="2" t="n"/>
     </row>
@@ -18037,31 +18037,31 @@
       </c>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>הרמ״ע מפאנו</t>
+          <t>שרה אמנו</t>
         </is>
       </c>
       <c r="E418" s="7" t="inlineStr">
         <is>
-          <t>The Teachings and Historical Influence of Rabbi Menachem Azariah of Pano</t>
+          <t>Sarah Our Matriarch:The Foundation of Prophecy and the Sovereignty of Spirit in the Tent and in Time</t>
         </is>
       </c>
       <c r="F418" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/coQyIiMtHho/edit</t>
+          <t>https://studio.youtube.com/video/QHHa6EXkb8U/edit</t>
         </is>
       </c>
       <c r="G418" s="7" t="inlineStr">
         <is>
-          <t>📜 The Rama of Fano (Rabbi Menachem Azariah) on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/439?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Sarah Our Matriarch on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/448?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H418" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/coQyIiMtHho</t>
+          <t>https://youtu.be/QHHa6EXkb8U</t>
         </is>
       </c>
       <c r="I418" s="2" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J418" s="2" t="n"/>
     </row>
@@ -18079,31 +18079,31 @@
       </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>חנה הנביאה</t>
+          <t>הרמ״ע מפאנו</t>
         </is>
       </c>
       <c r="E419" s="7" t="inlineStr">
         <is>
-          <t>Hannah’s Prayer: Faith, Halakha, and a Model for Education</t>
+          <t>The Teachings and Historical Influence of Rabbi Menachem Azariah of Pano</t>
         </is>
       </c>
       <c r="F419" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/uf6D-8ElhLQ/edit</t>
+          <t>https://studio.youtube.com/video/coQyIiMtHho/edit</t>
         </is>
       </c>
       <c r="G419" s="7" t="inlineStr">
         <is>
-          <t>📜 Hannah the Prophetess on Ozar Chachamim — the full research and a quiz: https://ozar-chachamim-app.vercel.app/en/sage/282?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 The Rama of Fano (Rabbi Menachem Azariah) on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/439?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H419" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/uf6D-8ElhLQ</t>
+          <t>https://youtu.be/coQyIiMtHho</t>
         </is>
       </c>
       <c r="I419" s="2" t="n">
-        <v>262</v>
+        <v>185</v>
       </c>
       <c r="J419" s="2" t="n"/>
     </row>
@@ -18121,31 +18121,31 @@
       </c>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>רבי יהונתן הכהן מלוניל</t>
+          <t>חנה הנביאה</t>
         </is>
       </c>
       <c r="E420" s="7" t="inlineStr">
         <is>
-          <t>The Great Luminary of Lunel: The Sage Who Brought Maimonides to Europe</t>
+          <t>Hannah’s Prayer: Faith, Halakha, and a Model for Education</t>
         </is>
       </c>
       <c r="F420" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/YxI2_lApcDI/edit</t>
+          <t>https://studio.youtube.com/video/uf6D-8ElhLQ/edit</t>
         </is>
       </c>
       <c r="G420" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Yehonatan HaKohen of Lunel on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/278?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Hannah the Prophetess on Ozar Chachamim — the full research and a quiz: https://ozar-chachamim-app.vercel.app/en/sage/282?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H420" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/YxI2_lApcDI</t>
+          <t>https://youtu.be/uf6D-8ElhLQ</t>
         </is>
       </c>
       <c r="I420" s="2" t="n">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J420" s="2" t="n"/>
     </row>
@@ -18163,31 +18163,31 @@
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>הרב שלמה זלמן אויערבך</t>
+          <t>רבי יהונתן הכהן מלוניל</t>
         </is>
       </c>
       <c r="E421" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Shlomo Zalman Auerbach: A Leading Halachic Authority in the Modern Era</t>
+          <t>The Great Luminary of Lunel: The Sage Who Brought Maimonides to Europe</t>
         </is>
       </c>
       <c r="F421" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/WvYmgdvQa2M/edit</t>
+          <t>https://studio.youtube.com/video/YxI2_lApcDI/edit</t>
         </is>
       </c>
       <c r="G421" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Shlomo Zalman Auerbach on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/157?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Yehonatan HaKohen of Lunel on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/278?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H421" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/WvYmgdvQa2M</t>
+          <t>https://youtu.be/YxI2_lApcDI</t>
         </is>
       </c>
       <c r="I421" s="2" t="n">
-        <v>391</v>
+        <v>267</v>
       </c>
       <c r="J421" s="2" t="n"/>
     </row>
@@ -18205,31 +18205,31 @@
       </c>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>הרב אפרים נבון (1677–1735) – מחנה אפרים: עקרונות פסיקה וסדרי קניינים</t>
+          <t>הרב שלמה זלמן אויערבך</t>
         </is>
       </c>
       <c r="E422" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Ephraim Navon and Machaneh Ephraim</t>
+          <t>Rabbi Shlomo Zalman Auerbach: A Leading Halachic Authority in the Modern Era</t>
         </is>
       </c>
       <c r="F422" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/_8SN0I-7CoY/edit</t>
+          <t>https://studio.youtube.com/video/WvYmgdvQa2M/edit</t>
         </is>
       </c>
       <c r="G422" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Ephraim Navon on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/87?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Shlomo Zalman Auerbach on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/157?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H422" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/_8SN0I-7CoY</t>
+          <t>https://youtu.be/WvYmgdvQa2M</t>
         </is>
       </c>
       <c r="I422" s="2" t="n">
-        <v>521</v>
+        <v>391</v>
       </c>
       <c r="J422" s="2" t="n"/>
     </row>
@@ -18247,31 +18247,31 @@
       </c>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>הרב יצחק אבוהב</t>
+          <t>הרב אפרים נבון (1677–1735) – מחנה אפרים: עקרונות פסיקה וסדרי קניינים</t>
         </is>
       </c>
       <c r="E423" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Yitzhak Abuhav – The Light of Generations, Author of “Menorat Ha-Maor”</t>
+          <t>Rabbi Ephraim Navon and Machaneh Ephraim</t>
         </is>
       </c>
       <c r="F423" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/L03uSsP6N4E/edit</t>
+          <t>https://studio.youtube.com/video/_8SN0I-7CoY/edit</t>
         </is>
       </c>
       <c r="G423" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Yitzchak Aboab on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/62?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Ephraim Navon on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/87?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H423" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/L03uSsP6N4E</t>
+          <t>https://youtu.be/_8SN0I-7CoY</t>
         </is>
       </c>
       <c r="I423" s="2" t="n">
-        <v>604</v>
+        <v>521</v>
       </c>
       <c r="J423" s="2" t="n"/>
     </row>
@@ -18284,36 +18284,36 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D424" s="4" t="inlineStr">
         <is>
-          <t>רבי אפרים אנקווה – 'הרב הרוכב על האריה'</t>
+          <t>הרב יצחק אבוהב</t>
         </is>
       </c>
       <c r="E424" s="7" t="inlineStr">
         <is>
-          <t>Рав Эфраим Анкава: жизнь и деятельность</t>
+          <t>Rabbi Yitzhak Abuhav – The Light of Generations, Author of “Menorat Ha-Maor”</t>
         </is>
       </c>
       <c r="F424" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/4A2JxVeX8Yc/edit</t>
+          <t>https://studio.youtube.com/video/L03uSsP6N4E/edit</t>
         </is>
       </c>
       <c r="G424" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Эфраим Анкава в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/58?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Yitzchak Aboab on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/62?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H424" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/4A2JxVeX8Yc</t>
+          <t>https://youtu.be/L03uSsP6N4E</t>
         </is>
       </c>
       <c r="I424" s="2" t="n">
-        <v>672</v>
+        <v>604</v>
       </c>
       <c r="J424" s="2" t="n"/>
     </row>
@@ -18326,36 +18326,36 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>שמואל (האמורא)</t>
+          <t>רבי אפרים אנקווה – 'הרב הרוכב על האריה'</t>
         </is>
       </c>
       <c r="E425" s="7" t="inlineStr">
         <is>
-          <t>Shmuel: His Legal Rulings and Teachings</t>
+          <t>Рав Эфраим Анкава: жизнь и деятельность</t>
         </is>
       </c>
       <c r="F425" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/6UfjwSUASjI/edit</t>
+          <t>https://studio.youtube.com/video/4A2JxVeX8Yc/edit</t>
         </is>
       </c>
       <c r="G425" s="7" t="inlineStr">
         <is>
-          <t>📜 Shmuel (the Amora) on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/482?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Эфраим Анкава в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/58?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H425" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/6UfjwSUASjI</t>
+          <t>https://youtu.be/4A2JxVeX8Yc</t>
         </is>
       </c>
       <c r="I425" s="2" t="n">
-        <v>692</v>
+        <v>672</v>
       </c>
       <c r="J425" s="2" t="n"/>
     </row>
@@ -18364,40 +18364,40 @@
         <v>425</v>
       </c>
       <c r="B426" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D426" s="4" t="inlineStr">
         <is>
-          <t>הרבנית חיה מושקא שניאורסון</t>
+          <t>שמואל (האמורא)</t>
         </is>
       </c>
       <c r="E426" s="7" t="inlineStr">
         <is>
-          <t>Ребецн Хая-Мушка Шнеерсон - духовное партнерство, самоотверженность и тихое лидерство</t>
+          <t>Shmuel: His Legal Rulings and Teachings</t>
         </is>
       </c>
       <c r="F426" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/vfjBSPWJqe4/edit</t>
+          <t>https://studio.youtube.com/video/6UfjwSUASjI/edit</t>
         </is>
       </c>
       <c r="G426" s="7" t="inlineStr">
         <is>
-          <t>📜 Ребецн Хая Мушка Шнеерсон в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/610?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Shmuel (the Amora) on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/482?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H426" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/vfjBSPWJqe4</t>
+          <t>https://youtu.be/6UfjwSUASjI</t>
         </is>
       </c>
       <c r="I426" s="2" t="n">
-        <v>95</v>
+        <v>692</v>
       </c>
       <c r="J426" s="2" t="n"/>
     </row>
@@ -18410,36 +18410,36 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>רבי שמשון בן אליעזר (ברוך שאמר)</t>
+          <t>הרבנית חיה מושקא שניאורסון</t>
         </is>
       </c>
       <c r="E427" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Samson ben Eliezer and the Tradition of Scribal Writing (STaM) in the Book "Baruch She’amar"</t>
+          <t>Ребецн Хая-Мушка Шнеерсон - духовное партнерство, самоотверженность и тихое лидерство</t>
         </is>
       </c>
       <c r="F427" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/nJQ_RbQIEvI/edit</t>
+          <t>https://studio.youtube.com/video/vfjBSPWJqe4/edit</t>
         </is>
       </c>
       <c r="G427" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Shimshon ben Eliezer (Baruch She'amar) on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/426?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Ребецн Хая Мушка Шнеерсон в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/610?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H427" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/nJQ_RbQIEvI</t>
+          <t>https://youtu.be/vfjBSPWJqe4</t>
         </is>
       </c>
       <c r="I427" s="2" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="J427" s="2" t="n"/>
     </row>
@@ -18457,31 +18457,31 @@
       </c>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>רבי נחמן קרוכמל (רנ״ק)</t>
+          <t>רבי שמשון בן אליעזר (ברוך שאמר)</t>
         </is>
       </c>
       <c r="E428" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Nachman Krochmal (RaNaK) – The Thinker Who Turned History into Proof of the Eternity of Israel</t>
+          <t>Rabbi Samson ben Eliezer and the Tradition of Scribal Writing (STaM) in the Book "Baruch She’amar"</t>
         </is>
       </c>
       <c r="F428" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/oAjWELNrN0I/edit</t>
+          <t>https://studio.youtube.com/video/nJQ_RbQIEvI/edit</t>
         </is>
       </c>
       <c r="G428" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Nachman Krochmal (Ranak) on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/315?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Shimshon ben Eliezer (Baruch She'amar) on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/426?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H428" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/oAjWELNrN0I</t>
+          <t>https://youtu.be/nJQ_RbQIEvI</t>
         </is>
       </c>
       <c r="I428" s="2" t="n">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="J428" s="2" t="n"/>
     </row>
@@ -18494,36 +18494,36 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>רבי יהודה הנשיא</t>
+          <t>רבי נחמן קרוכמל (רנ״ק)</t>
         </is>
       </c>
       <c r="E429" s="7" t="inlineStr">
         <is>
-          <t>Рабби Йеуда ха-Наси: между завершением Мишны и руководством народом</t>
+          <t>Rabbi Nachman Krochmal (RaNaK) – The Thinker Who Turned History into Proof of the Eternity of Israel</t>
         </is>
       </c>
       <c r="F429" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/lik5L505iH0/edit</t>
+          <t>https://studio.youtube.com/video/oAjWELNrN0I/edit</t>
         </is>
       </c>
       <c r="G429" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Йехуда ха-Наси в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/580?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Nachman Krochmal (Ranak) on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/315?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H429" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/lik5L505iH0</t>
+          <t>https://youtu.be/oAjWELNrN0I</t>
         </is>
       </c>
       <c r="I429" s="2" t="n">
-        <v>358</v>
+        <v>221</v>
       </c>
       <c r="J429" s="2" t="n"/>
     </row>
@@ -18536,36 +18536,36 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>רבי משה מקוצי (הסמ"ג)</t>
+          <t>רבי יהודה הנשיא</t>
         </is>
       </c>
       <c r="E430" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Moses of Coucy – the man who saw the Talmud burned and built a tower from it</t>
+          <t>Рабби Йеуда ха-Наси: между завершением Мишны и руководством народом</t>
         </is>
       </c>
       <c r="F430" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/diLTJBy2Jag/edit</t>
+          <t>https://studio.youtube.com/video/lik5L505iH0/edit</t>
         </is>
       </c>
       <c r="G430" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Moshe of Coucy (the Semag) on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/588?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Йехуда ха-Наси в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/580?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H430" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/diLTJBy2Jag</t>
+          <t>https://youtu.be/lik5L505iH0</t>
         </is>
       </c>
       <c r="I430" s="2" t="n">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="J430" s="2" t="n"/>
     </row>
@@ -18578,36 +18578,36 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>רבי יעקב אבן חביב (עין יעקב)</t>
+          <t>רבי משה מקוצי (הסמ"ג)</t>
         </is>
       </c>
       <c r="E431" s="7" t="inlineStr">
         <is>
-          <t>«Эйн Яаков»: мир и наследие рабби Яакова ибн Хабиба</t>
+          <t>Rabbi Moses of Coucy – the man who saw the Talmud burned and built a tower from it</t>
         </is>
       </c>
       <c r="F431" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/3RaB87PhVjs/edit</t>
+          <t>https://studio.youtube.com/video/diLTJBy2Jag/edit</t>
         </is>
       </c>
       <c r="G431" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Яаков ибн Хавив («Эйн Яаков») в «Оцар Хахамим» — полное исследование и его ученики: https://ozar-chachamim-app.vercel.app/ru/sage/603?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Moshe of Coucy (the Semag) on Ozar Chachamim — the full research and his teachers and students: https://ozar-chachamim-app.vercel.app/en/sage/588?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H431" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/3RaB87PhVjs</t>
+          <t>https://youtu.be/diLTJBy2Jag</t>
         </is>
       </c>
       <c r="I431" s="2" t="n">
-        <v>442</v>
+        <v>363</v>
       </c>
       <c r="J431" s="2" t="n"/>
     </row>
@@ -18625,31 +18625,31 @@
       </c>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>פרנץ רוזנצווייג – הפילוסוף שהחזיר את האדם למרכז</t>
+          <t>רבי יעקב אבן חביב (עין יעקב)</t>
         </is>
       </c>
       <c r="E432" s="7" t="inlineStr">
         <is>
-          <t>Франц Розенцвейг и его учение: иудейская теология и философия</t>
+          <t>«Эйн Яаков»: мир и наследие рабби Яакова ибн Хабиба</t>
         </is>
       </c>
       <c r="F432" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/fF1fkXyG-IU/edit</t>
+          <t>https://studio.youtube.com/video/3RaB87PhVjs/edit</t>
         </is>
       </c>
       <c r="G432" s="7" t="inlineStr">
         <is>
-          <t>📜 Франц Розенцвейг в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/141?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Яаков ибн Хавив («Эйн Яаков») в «Оцар Хахамим» — полное исследование и его ученики: https://ozar-chachamim-app.vercel.app/ru/sage/603?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H432" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/fF1fkXyG-IU</t>
+          <t>https://youtu.be/3RaB87PhVjs</t>
         </is>
       </c>
       <c r="I432" s="2" t="n">
-        <v>477</v>
+        <v>442</v>
       </c>
       <c r="J432" s="2" t="n"/>
     </row>
@@ -18662,36 +18662,36 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>רבי מרדכי יפה – “בעל הלבוש”</t>
+          <t>פרנץ רוזנצווייג – הפילוסוף שהחזיר את האדם למרכז</t>
         </is>
       </c>
       <c r="E433" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Yaffe and the Architecture of the Golden Age</t>
+          <t>Франц Розенцвейг и его учение: иудейская теология и философия</t>
         </is>
       </c>
       <c r="F433" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/I4iSync7vvQ/edit</t>
+          <t>https://studio.youtube.com/video/fF1fkXyG-IU/edit</t>
         </is>
       </c>
       <c r="G433" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Mordechai Yaffe (the Ba'al ha-Levushim) on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/73?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Франц Розенцвейг в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/141?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H433" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/I4iSync7vvQ</t>
+          <t>https://youtu.be/fF1fkXyG-IU</t>
         </is>
       </c>
       <c r="I433" s="2" t="n">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="J433" s="2" t="n"/>
     </row>
@@ -18709,31 +18709,31 @@
       </c>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>חכמי פרובנס – בין נרבון, בית דוד והמיסטיקה הראשונה: המרכז היהודי ששבר את המפה הרוחנית של ימי הביניים</t>
+          <t>רבי מרדכי יפה – “בעל הלבוש”</t>
         </is>
       </c>
       <c r="E434" s="7" t="inlineStr">
         <is>
-          <t>The Sages of Provence: Renaissance, Kabbalah, and Philosophy</t>
+          <t>Rabbi Yaffe and the Architecture of the Golden Age</t>
         </is>
       </c>
       <c r="F434" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/eGf4x9EmZPY/edit</t>
+          <t>https://studio.youtube.com/video/I4iSync7vvQ/edit</t>
         </is>
       </c>
       <c r="G434" s="7" t="inlineStr">
         <is>
-          <t>📜 The Sages of Provence on Ozar Chachamim — the page: https://ozar-chachamim-app.vercel.app/en/sage/38?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Mordechai Yaffe (the Ba'al ha-Levushim) on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/73?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H434" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/eGf4x9EmZPY</t>
+          <t>https://youtu.be/I4iSync7vvQ</t>
         </is>
       </c>
       <c r="I434" s="2" t="n">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="J434" s="2" t="n"/>
     </row>
@@ -18751,31 +18751,31 @@
       </c>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>רבי משה חגיז – הקנאי הירושלמי שניסה להציל את היהדות מן הקריסה הפנימית</t>
+          <t>חכמי פרובנס – בין נרבון, בית דוד והמיסטיקה הראשונה: המרכז היהודי ששבר את המפה הרוחנית של ימי הביניים</t>
         </is>
       </c>
       <c r="E435" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Moshe Hagiz – The Jerusalem Zealot Who Tried to Save Judaism from Internal Collapse</t>
+          <t>The Sages of Provence: Renaissance, Kabbalah, and Philosophy</t>
         </is>
       </c>
       <c r="F435" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/TBMI1NhMLYM/edit</t>
+          <t>https://studio.youtube.com/video/eGf4x9EmZPY/edit</t>
         </is>
       </c>
       <c r="G435" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Moshe Hagiz on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/86?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 The Sages of Provence on Ozar Chachamim — the page: https://ozar-chachamim-app.vercel.app/en/sage/38?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H435" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/TBMI1NhMLYM</t>
+          <t>https://youtu.be/eGf4x9EmZPY</t>
         </is>
       </c>
       <c r="I435" s="2" t="n">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="J435" s="2" t="n"/>
     </row>
@@ -18793,31 +18793,31 @@
       </c>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>דונש בן לברט</t>
+          <t>רבי משה חגיז – הקנאי הירושלמי שניסה להציל את היהדות מן הקריסה הפנימית</t>
         </is>
       </c>
       <c r="E436" s="7" t="inlineStr">
         <is>
-          <t>Dunash ben Labrat: His Life and Works</t>
+          <t>Rabbi Moshe Hagiz – The Jerusalem Zealot Who Tried to Save Judaism from Internal Collapse</t>
         </is>
       </c>
       <c r="F436" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/Nh2zBFGV2_Q/edit</t>
+          <t>https://studio.youtube.com/video/TBMI1NhMLYM/edit</t>
         </is>
       </c>
       <c r="G436" s="7" t="inlineStr">
         <is>
-          <t>📜 Dunash ben Labrat on Ozar Chachamim — the full research, a quiz, and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/198?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Moshe Hagiz on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/86?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H436" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/Nh2zBFGV2_Q</t>
+          <t>https://youtu.be/TBMI1NhMLYM</t>
         </is>
       </c>
       <c r="I436" s="2" t="n">
-        <v>659</v>
+        <v>506</v>
       </c>
       <c r="J436" s="2" t="n"/>
     </row>
@@ -18830,36 +18830,36 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>רבנו יונה גירונדי</t>
+          <t>דונש בן לברט</t>
         </is>
       </c>
       <c r="E437" s="7" t="inlineStr">
         <is>
-          <t>Рабейну Йона Гиронди: Тора, этика и полемика</t>
+          <t>Dunash ben Labrat: His Life and Works</t>
         </is>
       </c>
       <c r="F437" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/yCAH5_oIiX8/edit</t>
+          <t>https://studio.youtube.com/video/Nh2zBFGV2_Q/edit</t>
         </is>
       </c>
       <c r="G437" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабейну Йона Геронди в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/486?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Dunash ben Labrat on Ozar Chachamim — the full research, a quiz, and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/198?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H437" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/yCAH5_oIiX8</t>
+          <t>https://youtu.be/Nh2zBFGV2_Q</t>
         </is>
       </c>
       <c r="I437" s="2" t="n">
-        <v>703</v>
+        <v>659</v>
       </c>
       <c r="J437" s="2" t="n"/>
     </row>
@@ -18877,31 +18877,31 @@
       </c>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>הרב יצחק הוטנר</t>
+          <t>רבנו יונה גירונדי</t>
         </is>
       </c>
       <c r="E438" s="7" t="inlineStr">
         <is>
-          <t>Учение раввина Хутнера: «Пахад Ицхак» и «Даат»</t>
+          <t>Рабейну Йона Гиронди: Тора, этика и полемика</t>
         </is>
       </c>
       <c r="F438" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/vTYB_RodNy8/edit</t>
+          <t>https://studio.youtube.com/video/yCAH5_oIiX8/edit</t>
         </is>
       </c>
       <c r="G438" s="7" t="inlineStr">
         <is>
-          <t>📜 Рав Ицхак Хутнер в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/492?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабейну Йона Геронди в «Оцар Хахамим» — полное исследование, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/486?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H438" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/vTYB_RodNy8</t>
+          <t>https://youtu.be/yCAH5_oIiX8</t>
         </is>
       </c>
       <c r="I438" s="2" t="n">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="J438" s="2" t="n"/>
     </row>
@@ -18910,40 +18910,40 @@
         <v>438</v>
       </c>
       <c r="B439" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>רבי חנינא בר פפא</t>
+          <t>הרב יצחק הוטנר</t>
         </is>
       </c>
       <c r="E439" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Hanina bar Pappa - The Amora Who Asked the Angel of Death for 30 More Days</t>
+          <t>Учение раввина Хутнера: «Пахад Ицхак» и «Даат»</t>
         </is>
       </c>
       <c r="F439" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/xxmxesk4B6E/edit</t>
+          <t>https://studio.youtube.com/video/vTYB_RodNy8/edit</t>
         </is>
       </c>
       <c r="G439" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Chanina bar Pappa on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/543?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рав Ицхак Хутнер в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/492?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H439" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/xxmxesk4B6E</t>
+          <t>https://youtu.be/vTYB_RodNy8</t>
         </is>
       </c>
       <c r="I439" s="2" t="n">
-        <v>48</v>
+        <v>706</v>
       </c>
       <c r="J439" s="2" t="n"/>
     </row>
@@ -18956,36 +18956,36 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>רבן שמעון בן גמליאל הראשון</t>
+          <t>רבי חנינא בר פפא</t>
         </is>
       </c>
       <c r="E440" s="7" t="inlineStr">
         <is>
-          <t>Раббан Шимон бен Гамлиэль I - Наси, пытавшийся спасти Иерусалим накануне разрушения</t>
+          <t>Rabbi Hanina bar Pappa - The Amora Who Asked the Angel of Death for 30 More Days</t>
         </is>
       </c>
       <c r="F440" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/lVKW3ot6R5E/edit</t>
+          <t>https://studio.youtube.com/video/xxmxesk4B6E/edit</t>
         </is>
       </c>
       <c r="G440" s="7" t="inlineStr">
         <is>
-          <t>📜 Раббан Шимон бен Гамлиэль Первый в «Оцар Хахамим» — полное исследование и его ученики: https://ozar-chachamim-app.vercel.app/ru/sage/550?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Chanina bar Pappa on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/543?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H440" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/lVKW3ot6R5E</t>
+          <t>https://youtu.be/xxmxesk4B6E</t>
         </is>
       </c>
       <c r="I440" s="2" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="J440" s="2" t="n"/>
     </row>
@@ -19003,31 +19003,31 @@
       </c>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>רבן יוחנן בן זכאי</t>
+          <t>רבן שמעון בן גמליאל הראשון</t>
         </is>
       </c>
       <c r="E441" s="7" t="inlineStr">
         <is>
-          <t>Раббан Йоханан бен Заккай: руководство народом и Тора в эпоху разрушения и восстановления</t>
+          <t>Раббан Шимон бен Гамлиэль I - Наси, пытавшийся спасти Иерусалим накануне разрушения</t>
         </is>
       </c>
       <c r="F441" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/PSlsgd30bzQ/edit</t>
+          <t>https://studio.youtube.com/video/lVKW3ot6R5E/edit</t>
         </is>
       </c>
       <c r="G441" s="7" t="inlineStr">
         <is>
-          <t>📜 Раббан Йоханан бен Заккай в «Оцар Хахамим» — полное исследование, викторина, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/592?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Раббан Шимон бен Гамлиэль Первый в «Оцар Хахамим» — полное исследование и его ученики: https://ozar-chachamim-app.vercel.app/ru/sage/550?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H441" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/PSlsgd30bzQ</t>
+          <t>https://youtu.be/lVKW3ot6R5E</t>
         </is>
       </c>
       <c r="I441" s="2" t="n">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="J441" s="2" t="n"/>
     </row>
@@ -19040,36 +19040,36 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D442" s="4" t="inlineStr">
         <is>
-          <t>שרה אמנו</t>
+          <t>רבן יוחנן בן זכאי</t>
         </is>
       </c>
       <c r="E442" s="7" t="inlineStr">
         <is>
-          <t>Sarah Our Matriarch:The Foundation of Prophecy and the Sovereignty of Spirit in the Tent and in Time</t>
+          <t>Раббан Йоханан бен Заккай: руководство народом и Тора в эпоху разрушения и восстановления</t>
         </is>
       </c>
       <c r="F442" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/QHHa6EXkb8U/edit</t>
+          <t>https://studio.youtube.com/video/PSlsgd30bzQ/edit</t>
         </is>
       </c>
       <c r="G442" s="7" t="inlineStr">
         <is>
-          <t>📜 Sarah Our Matriarch on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/448?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Раббан Йоханан бен Заккай в «Оцар Хахамим» — полное исследование, викторина, а также его учителя и ученики: https://ozar-chachamim-app.vercel.app/ru/sage/592?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H442" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/QHHa6EXkb8U</t>
+          <t>https://youtu.be/PSlsgd30bzQ</t>
         </is>
       </c>
       <c r="I442" s="2" t="n">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="J442" s="2" t="n"/>
     </row>
@@ -19885,31 +19885,31 @@
       </c>
       <c r="D462" s="4" t="inlineStr">
         <is>
-          <t>הרב כלפון משה הכהן (1874–1950) – רב ג'רבא: הלכה, הנהגה וציונות דתית בצפון אפריקה</t>
+          <t>הרב נתן צבי פינקל (הסבא מסלבודקה)</t>
         </is>
       </c>
       <c r="E462" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Khalfon: Halakhic Decisor and Zionist Leader</t>
+          <t>The Grandfather of Slabodka and the Kingdom of Human Greatness: From Lithuania to Hebron &amp; Jerusalem</t>
         </is>
       </c>
       <c r="F462" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/rrilooQ8bSw/edit</t>
+          <t>https://studio.youtube.com/video/XqiW1-Q_dkY/edit</t>
         </is>
       </c>
       <c r="G462" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Khalfon Moshe HaKohen on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/136?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Nosson Tzvi Finkel (the Alter of Slabodka) on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/324?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H462" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/rrilooQ8bSw</t>
+          <t>https://youtu.be/XqiW1-Q_dkY</t>
         </is>
       </c>
       <c r="I462" s="2" t="n">
-        <v>538</v>
+        <v>341</v>
       </c>
       <c r="J462" s="2" t="n"/>
     </row>
@@ -19927,31 +19927,31 @@
       </c>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>הרב מאיר זייני</t>
+          <t>הרב כלפון משה הכהן (1874–1950) – רב ג'רבא: הלכה, הנהגה וציונות דתית בצפון אפריקה</t>
         </is>
       </c>
       <c r="E463" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Meir Zini: The Heroic Leader Bridging Algeria, Auschwitz, and Montmartre</t>
+          <t>Rabbi Khalfon: Halakhic Decisor and Zionist Leader</t>
         </is>
       </c>
       <c r="F463" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/TRDE4AG2kLE/edit</t>
+          <t>https://studio.youtube.com/video/rrilooQ8bSw/edit</t>
         </is>
       </c>
       <c r="G463" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Meir Zeini on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/165?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Khalfon Moshe HaKohen on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/136?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H463" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/TRDE4AG2kLE</t>
+          <t>https://youtu.be/rrilooQ8bSw</t>
         </is>
       </c>
       <c r="I463" s="2" t="n">
-        <v>597</v>
+        <v>538</v>
       </c>
       <c r="J463" s="2" t="n"/>
     </row>
@@ -19964,36 +19964,36 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>רבי רפאל משה לוריא</t>
+          <t>הרב מאיר זייני</t>
         </is>
       </c>
       <c r="E464" s="7" t="inlineStr">
         <is>
-          <t>Раввин Моше Лурия: каббалист и учёный</t>
+          <t>Rabbi Meir Zini: The Heroic Leader Bridging Algeria, Auschwitz, and Montmartre</t>
         </is>
       </c>
       <c r="F464" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/OvfCDsr2-p4/edit</t>
+          <t>https://studio.youtube.com/video/TRDE4AG2kLE/edit</t>
         </is>
       </c>
       <c r="G464" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Рефаэль Моше Лурия в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/174?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Meir Zeini on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/165?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H464" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/OvfCDsr2-p4</t>
+          <t>https://youtu.be/TRDE4AG2kLE</t>
         </is>
       </c>
       <c r="I464" s="2" t="n">
-        <v>621</v>
+        <v>597</v>
       </c>
       <c r="J464" s="2" t="n"/>
     </row>
@@ -20006,36 +20006,36 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>רבי יוסף טאיטצאק – המקובל שחזה את הציונות</t>
+          <t>רבי רפאל משה לוריא</t>
         </is>
       </c>
       <c r="E465" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Yosef Taitatzak - The Kabbalist Who Foresaw Zionism</t>
+          <t>Раввин Моше Лурия: каббалист и учёный</t>
         </is>
       </c>
       <c r="F465" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/sCJ-e_Ggy68/edit</t>
+          <t>https://studio.youtube.com/video/OvfCDsr2-p4/edit</t>
         </is>
       </c>
       <c r="G465" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Yosef Taitazak on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/68?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Рефаэль Моше Лурия в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/174?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H465" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/sCJ-e_Ggy68</t>
+          <t>https://youtu.be/OvfCDsr2-p4</t>
         </is>
       </c>
       <c r="I465" s="2" t="n">
-        <v>673</v>
+        <v>621</v>
       </c>
       <c r="J465" s="2" t="n"/>
     </row>
@@ -20048,36 +20048,36 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>עברית</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D466" s="4" t="inlineStr">
         <is>
-          <t>חכם דוד ניטו</t>
-        </is>
-      </c>
-      <c r="E466" s="5" t="inlineStr">
-        <is>
-          <t>דוד ניטו: מטה דן ופולמוס הטבע</t>
+          <t>רבי יוסף טאיטצאק – המקובל שחזה את הציונות</t>
+        </is>
+      </c>
+      <c r="E466" s="7" t="inlineStr">
+        <is>
+          <t>Rabbi Yosef Taitatzak - The Kabbalist Who Foresaw Zionism</t>
         </is>
       </c>
       <c r="F466" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/dT4vX4G3LJk/edit</t>
-        </is>
-      </c>
-      <c r="G466" s="5" t="inlineStr">
-        <is>
-          <t>📜 חכם דוד ניטו באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/487?utm_source=youtube&amp;utm_medium=video</t>
+          <t>https://studio.youtube.com/video/sCJ-e_Ggy68/edit</t>
+        </is>
+      </c>
+      <c r="G466" s="7" t="inlineStr">
+        <is>
+          <t>📜 Rabbi Yosef Taitazak on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/68?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H466" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/dT4vX4G3LJk</t>
+          <t>https://youtu.be/sCJ-e_Ggy68</t>
         </is>
       </c>
       <c r="I466" s="2" t="n">
-        <v>729</v>
+        <v>673</v>
       </c>
       <c r="J466" s="2" t="n"/>
     </row>
@@ -20086,40 +20086,40 @@
         <v>466</v>
       </c>
       <c r="B467" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>עברית</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>רבי אברהם בן שלמה הלוי בוקראט</t>
-        </is>
-      </c>
-      <c r="E467" s="7" t="inlineStr">
-        <is>
-          <t>Rabbi Abraham Bokrat - The Scholar Expelled from Spain Who Rose to Rashi’s Defense</t>
+          <t>חכם דוד ניטו</t>
+        </is>
+      </c>
+      <c r="E467" s="5" t="inlineStr">
+        <is>
+          <t>דוד ניטו: מטה דן ופולמוס הטבע</t>
         </is>
       </c>
       <c r="F467" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/3tqZnY6xxJ4/edit</t>
-        </is>
-      </c>
-      <c r="G467" s="7" t="inlineStr">
-        <is>
-          <t>📜 Rabbi Abraham ben Solomon HaLevi Bokrat on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/627?utm_source=youtube&amp;utm_medium=video</t>
+          <t>https://studio.youtube.com/video/dT4vX4G3LJk/edit</t>
+        </is>
+      </c>
+      <c r="G467" s="5" t="inlineStr">
+        <is>
+          <t>📜 חכם דוד ניטו באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/487?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H467" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/3tqZnY6xxJ4</t>
+          <t>https://youtu.be/dT4vX4G3LJk</t>
         </is>
       </c>
       <c r="I467" s="2" t="n">
-        <v>8</v>
+        <v>729</v>
       </c>
       <c r="J467" s="2" t="n"/>
     </row>
@@ -20137,31 +20137,31 @@
       </c>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>הרבנית אסתר יונגרייז</t>
+          <t>רבי אברהם בן שלמה הלוי בוקראט</t>
         </is>
       </c>
       <c r="E468" s="7" t="inlineStr">
         <is>
-          <t>A Call from the Ashes: The Legacy of Rebbetzin Esther Jungreis and the Hineni Movement</t>
+          <t>Rabbi Abraham Bokrat - The Scholar Expelled from Spain Who Rose to Rashi’s Defense</t>
         </is>
       </c>
       <c r="F468" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/qr-Jzk95mEA/edit</t>
+          <t>https://studio.youtube.com/video/3tqZnY6xxJ4/edit</t>
         </is>
       </c>
       <c r="G468" s="7" t="inlineStr">
         <is>
-          <t>📜 Rebbetzin Esther Jungreis on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/514?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Abraham ben Solomon HaLevi Bokrat on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/627?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H468" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/qr-Jzk95mEA</t>
+          <t>https://youtu.be/3tqZnY6xxJ4</t>
         </is>
       </c>
       <c r="I468" s="2" t="n">
-        <v>115</v>
+        <v>8</v>
       </c>
       <c r="J468" s="2" t="n"/>
     </row>
@@ -20179,31 +20179,31 @@
       </c>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>שמאי הזקן</t>
+          <t>הרבנית אסתר יונגרייז</t>
         </is>
       </c>
       <c r="E469" s="7" t="inlineStr">
         <is>
-          <t>Shammai the Elder: His Character, Teachings, and the Legacy of the House of Shammai</t>
+          <t>A Call from the Ashes: The Legacy of Rebbetzin Esther Jungreis and the Hineni Movement</t>
         </is>
       </c>
       <c r="F469" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/TuIOTBpjNZE/edit</t>
+          <t>https://studio.youtube.com/video/qr-Jzk95mEA/edit</t>
         </is>
       </c>
       <c r="G469" s="7" t="inlineStr">
         <is>
-          <t>📜 Shammai the Elder on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/504?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rebbetzin Esther Jungreis on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/514?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H469" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/TuIOTBpjNZE</t>
+          <t>https://youtu.be/qr-Jzk95mEA</t>
         </is>
       </c>
       <c r="I469" s="2" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="J469" s="2" t="n"/>
     </row>
@@ -20216,36 +20216,36 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>Русский</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>רבינו דוד בונפיד</t>
+          <t>שמאי הזקן</t>
         </is>
       </c>
       <c r="E470" s="7" t="inlineStr">
         <is>
-          <t>Рав Давид Бонафед: ученик Рамбана и его духовное наследие в Испании</t>
+          <t>Shammai the Elder: His Character, Teachings, and the Legacy of the House of Shammai</t>
         </is>
       </c>
       <c r="F470" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/pGDFGE42KoM/edit</t>
+          <t>https://studio.youtube.com/video/TuIOTBpjNZE/edit</t>
         </is>
       </c>
       <c r="G470" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабейну Давид Бонафед в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/460?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Shammai the Elder on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/504?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H470" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/pGDFGE42KoM</t>
+          <t>https://youtu.be/TuIOTBpjNZE</t>
         </is>
       </c>
       <c r="I470" s="2" t="n">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="J470" s="2" t="n"/>
     </row>
@@ -20263,31 +20263,31 @@
       </c>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>רבי סעדיה שוראקי</t>
+          <t>רבינו דוד בונפיד</t>
         </is>
       </c>
       <c r="E471" s="7" t="inlineStr">
         <is>
-          <t>Рабби Саадия Шураки — раввин, который ввёл математику в дом учения</t>
+          <t>Рав Давид Бонафед: ученик Рамбана и его духовное наследие в Испании</t>
         </is>
       </c>
       <c r="F471" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/ZY7m_A8SBuA/edit</t>
+          <t>https://studio.youtube.com/video/pGDFGE42KoM/edit</t>
         </is>
       </c>
       <c r="G471" s="7" t="inlineStr">
         <is>
-          <t>📜 Рабби Саадья Шураки в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/277?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабейну Давид Бонафед в «Оцар Хахамим» — полное исследование и его учителя: https://ozar-chachamim-app.vercel.app/ru/sage/460?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H471" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/ZY7m_A8SBuA</t>
+          <t>https://youtu.be/pGDFGE42KoM</t>
         </is>
       </c>
       <c r="I471" s="2" t="n">
-        <v>269</v>
+        <v>167</v>
       </c>
       <c r="J471" s="2" t="n"/>
     </row>
@@ -20300,36 +20300,36 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Русский</t>
         </is>
       </c>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>רבי משה הדרשן</t>
+          <t>רבי סעדיה שוראקי</t>
         </is>
       </c>
       <c r="E472" s="7" t="inlineStr">
         <is>
-          <t>Rabbi Moshe HaDarshan – The Sage Who Shaped the World of Midrash in Europe</t>
+          <t>Рабби Саадия Шураки — раввин, который ввёл математику в дом учения</t>
         </is>
       </c>
       <c r="F472" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/B7dQL1mV29k/edit</t>
+          <t>https://studio.youtube.com/video/ZY7m_A8SBuA/edit</t>
         </is>
       </c>
       <c r="G472" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Moshe HaDarshan on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/348?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Рабби Саадья Шураки в «Оцар Хахамим» — полное исследование: https://ozar-chachamim-app.vercel.app/ru/sage/277?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H472" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/B7dQL1mV29k</t>
+          <t>https://youtu.be/ZY7m_A8SBuA</t>
         </is>
       </c>
       <c r="I472" s="2" t="n">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="J472" s="2" t="n"/>
     </row>
@@ -20347,31 +20347,31 @@
       </c>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>רבי דוד פארדו</t>
+          <t>רבי משה הדרשן</t>
         </is>
       </c>
       <c r="E473" s="7" t="inlineStr">
         <is>
-          <t>Rabbi David Pardo and the Revolution in Tosefta Interpretation in Chasdei David</t>
+          <t>Rabbi Moshe HaDarshan – The Sage Who Shaped the World of Midrash in Europe</t>
         </is>
       </c>
       <c r="F473" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/U6Jz3o9QeI0/edit</t>
+          <t>https://studio.youtube.com/video/B7dQL1mV29k/edit</t>
         </is>
       </c>
       <c r="G473" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi David Pardo on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/349?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi Moshe HaDarshan on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/348?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H473" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/U6Jz3o9QeI0</t>
+          <t>https://youtu.be/B7dQL1mV29k</t>
         </is>
       </c>
       <c r="I473" s="2" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="J473" s="2" t="n"/>
     </row>
@@ -20389,31 +20389,31 @@
       </c>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>רבנו בחיי בן אשר</t>
+          <t>רבי דוד פארדו</t>
         </is>
       </c>
       <c r="E474" s="7" t="inlineStr">
         <is>
-          <t>Rabbeinu  Bahya ben Asher: Between Peshat and Sod</t>
+          <t>Rabbi David Pardo and the Revolution in Tosefta Interpretation in Chasdei David</t>
         </is>
       </c>
       <c r="F474" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/A9WGoajqE-g/edit</t>
+          <t>https://studio.youtube.com/video/U6Jz3o9QeI0/edit</t>
         </is>
       </c>
       <c r="G474" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbenu Bachya ben Asher on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/12?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbi David Pardo on Ozar Chachamim — the full research: https://ozar-chachamim-app.vercel.app/en/sage/349?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H474" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/A9WGoajqE-g</t>
+          <t>https://youtu.be/U6Jz3o9QeI0</t>
         </is>
       </c>
       <c r="I474" s="2" t="n">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="J474" s="2" t="n"/>
     </row>
@@ -20431,31 +20431,31 @@
       </c>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>הרב נתן צבי פינקל (הסבא מסלבודקה)</t>
+          <t>רבנו בחיי בן אשר</t>
         </is>
       </c>
       <c r="E475" s="7" t="inlineStr">
         <is>
-          <t>The Grandfather of Slabodka and the Kingdom of Human Greatness: From Lithuania to Hebron &amp; Jerusalem</t>
+          <t>Rabbeinu  Bahya ben Asher: Between Peshat and Sod</t>
         </is>
       </c>
       <c r="F475" s="6" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/video/XqiW1-Q_dkY/edit</t>
+          <t>https://studio.youtube.com/video/A9WGoajqE-g/edit</t>
         </is>
       </c>
       <c r="G475" s="7" t="inlineStr">
         <is>
-          <t>📜 Rabbi Nosson Tzvi Finkel (the Alter of Slabodka) on Ozar Chachamim — the full research and his students: https://ozar-chachamim-app.vercel.app/en/sage/324?utm_source=youtube&amp;utm_medium=video</t>
+          <t>📜 Rabbenu Bachya ben Asher on Ozar Chachamim — the full research and his teachers: https://ozar-chachamim-app.vercel.app/en/sage/12?utm_source=youtube&amp;utm_medium=video</t>
         </is>
       </c>
       <c r="H475" s="6" t="inlineStr">
         <is>
-          <t>https://youtu.be/XqiW1-Q_dkY</t>
+          <t>https://youtu.be/A9WGoajqE-g</t>
         </is>
       </c>
       <c r="I475" s="2" t="n">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="J475" s="2" t="n"/>
     </row>
@@ -32491,7 +32491,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1885</v>
+        <v>1890</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>148</v>
@@ -32680,7 +32680,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>129</v>
@@ -32923,7 +32923,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>192</v>
@@ -33139,7 +33139,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>151</v>
@@ -33868,7 +33868,7 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>631</v>
@@ -34057,7 +34057,7 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>108</v>
@@ -34300,7 +34300,7 @@
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>17</v>
@@ -34624,7 +34624,7 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>180</v>
@@ -34853,24 +34853,24 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>יעקב בן אשר</t>
+          <t>אליהו בן אמוזג – ההוגה שדחו הדורות, אך רעיונו התגלה כגדול מדורותיו</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/1ascElHzBKieDVSWk8wZBw</t>
+          <t>https://open.spotify.com/episode/66ocgEWzF0dAp3RmcvYSAn</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>📜 יעקב בן אשר באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/189?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 אליהו בן אמוזג באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/118?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
         <v>145</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="G90" s="2" t="n"/>
     </row>
@@ -34880,24 +34880,24 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>רבי יוסף חיון (רי״ח)</t>
+          <t>יעקב בן אשר</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5J3m8GmCr0dbgQl0IyUyW6</t>
+          <t>https://open.spotify.com/episode/1ascElHzBKieDVSWk8wZBw</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי יוסף חיון (רי״ח) באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/19?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 יעקב בן אשר באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/189?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="G91" s="2" t="n"/>
     </row>
@@ -34907,24 +34907,24 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>אליהו בן אמוזג – ההוגה שדחו הדורות, אך רעיונו התגלה כגדול מדורותיו</t>
+          <t>רבי יוסף חיון (רי״ח)</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/66ocgEWzF0dAp3RmcvYSAn</t>
+          <t>https://open.spotify.com/episode/5J3m8GmCr0dbgQl0IyUyW6</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>📜 אליהו בן אמוזג באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/118?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי יוסף חיון (רי״ח) באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/19?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
         <v>144</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="G92" s="2" t="n"/>
     </row>
@@ -35299,7 +35299,7 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F106" s="2" t="n">
         <v>154</v>
@@ -35312,24 +35312,24 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>רבי שם טוב אבן גאון</t>
+          <t>פרנץ רוזנצווייג – הפילוסוף שהחזיר את האדם למרכז</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4WLBwaZKgmiVJPIACa5dJR</t>
+          <t>https://open.spotify.com/episode/7EpaIjYgIJVmSWDAsXDI7g</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי שם טוב אבן גאון באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/415?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 פרנץ רוזנצווייג באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/141?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
         <v>120</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>415</v>
+        <v>141</v>
       </c>
       <c r="G107" s="2" t="n"/>
     </row>
@@ -35339,24 +35339,24 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>האדמו"ר מפיאסצ'נה (1889–1942) – קודש בתוך החורבן: תורה פסיכולוגית, אמונה ועמידה בגטו ורשה</t>
+          <t>רבי שם טוב אבן גאון</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/462p60k0hrJUeoi1OiEtfD</t>
+          <t>https://open.spotify.com/episode/4WLBwaZKgmiVJPIACa5dJR</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>📜 האדמו״ר מפיאסצ׳נה באוצר חכמים — המחקר המלא וחידון: https://ozar-chachamim-app.vercel.app/he/sage/143?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי שם טוב אבן גאון באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/415?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>143</v>
+        <v>415</v>
       </c>
       <c r="G108" s="2" t="n"/>
     </row>
@@ -35366,24 +35366,24 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>אברהם בר חייא</t>
+          <t>האדמו"ר מפיאסצ'נה (1889–1942) – קודש בתוך החורבן: תורה פסיכולוגית, אמונה ועמידה בגטו ורשה</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/3FAGqYdzyMQbyPbon3KYoC</t>
+          <t>https://open.spotify.com/episode/462p60k0hrJUeoi1OiEtfD</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>📜 אברהם בר חייא באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/190?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 האדמו״ר מפיאסצ׳נה באוצר חכמים — המחקר המלא וחידון: https://ozar-chachamim-app.vercel.app/he/sage/143?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
         <v>118</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="G109" s="2" t="n"/>
     </row>
@@ -35393,24 +35393,24 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>רבי חנינא בר פפא</t>
+          <t>אברהם בר חייא</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/05UPnPXXJ2u149d7DKjKzG</t>
+          <t>https://open.spotify.com/episode/3FAGqYdzyMQbyPbon3KYoC</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי חנינא בר פפא באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/543?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 אברהם בר חייא באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/190?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
         <v>118</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>543</v>
+        <v>190</v>
       </c>
       <c r="G110" s="2" t="n"/>
     </row>
@@ -35420,24 +35420,24 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>רבי משה חיים לוצאטו (הרמח״ל)</t>
+          <t>רבי חנינא בר פפא</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/1lgKTjkSyrd7SAntCbBGTt</t>
+          <t>https://open.spotify.com/episode/05UPnPXXJ2u149d7DKjKzG</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי משה חיים לוצאטו (הרמח״ל) באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/93?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי חנינא בר פפא באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/543?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>93</v>
+        <v>543</v>
       </c>
       <c r="G111" s="2" t="n"/>
     </row>
@@ -35447,24 +35447,24 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>שמעון כיפא – מרטיר נוצרי או צדיק נסתר ששלחו חכמי ישראל?</t>
+          <t>רבי משה חיים לוצאטו (הרמח״ל)</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4tu43oeL4qVdXGKzX2025J</t>
+          <t>https://open.spotify.com/episode/1lgKTjkSyrd7SAntCbBGTt</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>📜 שמעון כיפא באוצר חכמים — הדף שלו: https://ozar-chachamim-app.vercel.app/he/sage/193?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי משה חיים לוצאטו (הרמח״ל) באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/93?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
         <v>117</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="G112" s="2" t="n"/>
     </row>
@@ -35474,24 +35474,24 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>פרנץ רוזנצווייג – הפילוסוף שהחזיר את האדם למרכז</t>
+          <t>שמעון כיפא – מרטיר נוצרי או צדיק נסתר ששלחו חכמי ישראל?</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7EpaIjYgIJVmSWDAsXDI7g</t>
+          <t>https://open.spotify.com/episode/4tu43oeL4qVdXGKzX2025J</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>📜 פרנץ רוזנצווייג באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/141?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 שמעון כיפא באוצר חכמים — הדף שלו: https://ozar-chachamim-app.vercel.app/he/sage/193?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>141</v>
+        <v>193</v>
       </c>
       <c r="G113" s="2" t="n"/>
     </row>
@@ -35555,24 +35555,24 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>רבי יחיאל מפריז</t>
+          <t>ילקוט שמעוני</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/46MHn4vu6ORF3S4hyf9rN9</t>
+          <t>https://open.spotify.com/episode/7tKvMKCTFSZebvK2vj0U5b</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי יחיאל מפריז באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/54?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 ילקוט שמעוני באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/55?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G116" s="2" t="n"/>
     </row>
@@ -35582,24 +35582,24 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>ילקוט שמעוני</t>
+          <t>רבי יחיאל מפריז</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7tKvMKCTFSZebvK2vj0U5b</t>
+          <t>https://open.spotify.com/episode/46MHn4vu6ORF3S4hyf9rN9</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>📜 ילקוט שמעוני באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/55?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי יחיאל מפריז באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/54?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
         <v>111</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G117" s="2" t="n"/>
     </row>
@@ -36149,24 +36149,24 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>רבי שמשון בן צדוק</t>
+          <t>הרב שמואל בורנשטיין – בעל 'שם משמואל'</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5icFLQJoUIWSCfgYau1reF</t>
+          <t>https://open.spotify.com/episode/5dTIktS4k7pzb2kSQbqtXB</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי שמשון בן צדוק באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/317?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 הרב שמואל בורנשטיין באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/131?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E138" s="3" t="n">
         <v>94</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>317</v>
+        <v>131</v>
       </c>
       <c r="G138" s="2" t="n"/>
     </row>
@@ -36176,24 +36176,24 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>רבנו תם (ר׳ יעקב בן מאיר) – מהפכן השיטה התוספתית</t>
+          <t>רבי שמשון בן צדוק</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5u9zxyAssijvwzZnbKM7OQ</t>
+          <t>https://open.spotify.com/episode/5icFLQJoUIWSCfgYau1reF</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>📜 רבנו תם (ר׳ יעקב בן מאיר) באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/33?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי שמשון בן צדוק באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/317?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>33</v>
+        <v>317</v>
       </c>
       <c r="G139" s="2" t="n"/>
     </row>
@@ -36203,24 +36203,24 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>רבי יצחק סגי נהור</t>
+          <t>רבנו תם (ר׳ יעקב בן מאיר) – מהפכן השיטה התוספתית</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/16NM4luayYQvcaoGO21kWg</t>
+          <t>https://open.spotify.com/episode/5u9zxyAssijvwzZnbKM7OQ</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי יצחק סגי נהור באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/42?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבנו תם (ר׳ יעקב בן מאיר) באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/33?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E140" s="3" t="n">
         <v>93</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G140" s="2" t="n"/>
     </row>
@@ -36230,24 +36230,24 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>הרב שמואל בורנשטיין – בעל 'שם משמואל'</t>
+          <t>רבי יצחק סגי נהור</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5dTIktS4k7pzb2kSQbqtXB</t>
+          <t>https://open.spotify.com/episode/16NM4luayYQvcaoGO21kWg</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>📜 הרב שמואל בורנשטיין באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/131?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי יצחק סגי נהור באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/42?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E141" s="3" t="n">
         <v>93</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>131</v>
+        <v>42</v>
       </c>
       <c r="G141" s="2" t="n"/>
     </row>
@@ -36608,24 +36608,24 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>תודוס איש רומי</t>
+          <t>רבי אלעזר מגרמייזא (בעל הרוקח)</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5FpiW245vsxYv7x3SXzLgq</t>
+          <t>https://open.spotify.com/episode/1xnTTOc3bgPDd10LUBerVb</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>📜 תודוס איש רומי באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/485?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי אלעזר מגרמייזא (בעל הרוקח) באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/280?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E155" s="3" t="n">
         <v>78</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>485</v>
+        <v>280</v>
       </c>
       <c r="G155" s="2" t="n"/>
     </row>
@@ -36635,24 +36635,24 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>רבי יהודה החסיד (חסידי אשכנז)</t>
+          <t>תודוס איש רומי</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/70SOBeANLpCEBeEplD3eOw</t>
+          <t>https://open.spotify.com/episode/5FpiW245vsxYv7x3SXzLgq</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי יהודה החסיד (חסידי אשכנז) באוצר חכמים — המחקר המלא ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/11?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 תודוס איש רומי באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/485?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>11</v>
+        <v>485</v>
       </c>
       <c r="G156" s="2" t="n"/>
     </row>
@@ -36662,24 +36662,24 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>רבי אפרים אנקווה – 'הרב הרוכב על האריה'</t>
+          <t>רבי יהודה החסיד (חסידי אשכנז)</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/7q3U1w91U94YzhWhEWkgSB</t>
+          <t>https://open.spotify.com/episode/70SOBeANLpCEBeEplD3eOw</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי אפרים אנקווה באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/58?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי יהודה החסיד (חסידי אשכנז) באוצר חכמים — המחקר המלא ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/11?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E157" s="3" t="n">
         <v>77</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="G157" s="2" t="n"/>
     </row>
@@ -36689,24 +36689,24 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>רבי אלעזר מגרמייזא (בעל הרוקח)</t>
+          <t>רבי אפרים אנקווה – 'הרב הרוכב על האריה'</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/1xnTTOc3bgPDd10LUBerVb</t>
+          <t>https://open.spotify.com/episode/7q3U1w91U94YzhWhEWkgSB</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי אלעזר מגרמייזא (בעל הרוקח) באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/280?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי אפרים אנקווה באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/58?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E158" s="3" t="n">
         <v>77</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>280</v>
+        <v>58</v>
       </c>
       <c r="G158" s="2" t="n"/>
     </row>
@@ -38795,24 +38795,24 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>רבי אלעזר בן עזריה</t>
+          <t>הרב נתן צבי פינקל (הסבא מסלבודקה)</t>
         </is>
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/581Qie3gJwcdnadi7wnNF2</t>
+          <t>https://open.spotify.com/episode/4iRZ0WdzCGhxJrGTmkAzUf</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי אלעזר בן עזריה באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/506?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 הרב נתן צבי פינקל (הסבא מסלבודקה) באוצר חכמים — המחקר המלא ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/324?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E236" s="3" t="n">
         <v>44</v>
       </c>
       <c r="F236" s="2" t="n">
-        <v>506</v>
+        <v>324</v>
       </c>
       <c r="G236" s="2" t="n"/>
     </row>
@@ -38822,24 +38822,24 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>רבי שמעון לביא</t>
+          <t>רבי אלעזר בן עזריה</t>
         </is>
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/09sbxccxPcM8mqxUj6yDR4</t>
+          <t>https://open.spotify.com/episode/581Qie3gJwcdnadi7wnNF2</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי שמעון לביא באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/14?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי אלעזר בן עזריה באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/506?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>14</v>
+        <v>506</v>
       </c>
       <c r="G237" s="2" t="n"/>
     </row>
@@ -38849,24 +38849,24 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>הרב נתן צבי פינקל (הסבא מסלבודקה)</t>
+          <t>רבי שמעון לביא</t>
         </is>
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4iRZ0WdzCGhxJrGTmkAzUf</t>
+          <t>https://open.spotify.com/episode/09sbxccxPcM8mqxUj6yDR4</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>📜 הרב נתן צבי פינקל (הסבא מסלבודקה) באוצר חכמים — המחקר המלא ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/324?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי שמעון לביא באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/14?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E238" s="3" t="n">
         <v>43</v>
       </c>
       <c r="F238" s="2" t="n">
-        <v>324</v>
+        <v>14</v>
       </c>
       <c r="G238" s="2" t="n"/>
     </row>
@@ -39686,24 +39686,24 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>רבי יהושע בן חנניה</t>
+          <t>שרה אמנו</t>
         </is>
       </c>
       <c r="C269" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4GuQl9XmYIYRZ48ooTWu4Q</t>
+          <t>https://open.spotify.com/episode/2XYXmPscJIo8gLmJov6AFc</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי יהושע בן חנניה באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/503?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 שרה אמנו באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/448?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E269" s="3" t="n">
         <v>32</v>
       </c>
       <c r="F269" s="2" t="n">
-        <v>503</v>
+        <v>448</v>
       </c>
       <c r="G269" s="2" t="n"/>
     </row>
@@ -39713,24 +39713,24 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>אדולף פראנק – הקבלה כפילוסופיה דתית</t>
+          <t>רבי יהושע בן חנניה</t>
         </is>
       </c>
       <c r="C270" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/5qiFDQTROpb7v21w4imqIE</t>
+          <t>https://open.spotify.com/episode/4GuQl9XmYIYRZ48ooTWu4Q</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>📜 אדולף פראנק באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/114?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי יהושע בן חנניה באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/503?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E270" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F270" s="2" t="n">
-        <v>114</v>
+        <v>503</v>
       </c>
       <c r="G270" s="2" t="n"/>
     </row>
@@ -39740,24 +39740,24 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>הרב משה־צבי נריה – המהפכן הציוני־דתי שחי כל חייו בין חזון ל"בדיעבד" כעבודה: כשהעשייה היא דרך המלך</t>
+          <t>אדולף פראנק – הקבלה כפילוסופיה דתית</t>
         </is>
       </c>
       <c r="C271" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/43IiFgqfBCu9lLZIR07if7</t>
+          <t>https://open.spotify.com/episode/5qiFDQTROpb7v21w4imqIE</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>📜 הרב משה־צבי נריה באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/159?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 אדולף פראנק באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/114?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E271" s="3" t="n">
         <v>31</v>
       </c>
       <c r="F271" s="2" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="G271" s="2" t="n"/>
     </row>
@@ -39767,24 +39767,24 @@
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>אסתר המלכה</t>
+          <t>הרב משה־צבי נריה – המהפכן הציוני־דתי שחי כל חייו בין חזון ל"בדיעבד" כעבודה: כשהעשייה היא דרך המלך</t>
         </is>
       </c>
       <c r="C272" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/4WssFuGXzvEgr2GstxIHfx</t>
+          <t>https://open.spotify.com/episode/43IiFgqfBCu9lLZIR07if7</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>📜 אסתר המלכה באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/268?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 הרב משה־צבי נריה באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/159?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E272" s="3" t="n">
         <v>31</v>
       </c>
       <c r="F272" s="2" t="n">
-        <v>268</v>
+        <v>159</v>
       </c>
       <c r="G272" s="2" t="n"/>
     </row>
@@ -39794,24 +39794,24 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>החיד״א (רבי חיים יוסף דוד אזולאי)</t>
+          <t>אסתר המלכה</t>
         </is>
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/2MiUUx51sCblnVdS9i61Xq</t>
+          <t>https://open.spotify.com/episode/4WssFuGXzvEgr2GstxIHfx</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>📜 החיד״א (רבי חיים יוסף דוד אזולאי) באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/325?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 אסתר המלכה באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/268?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E273" s="3" t="n">
         <v>31</v>
       </c>
       <c r="F273" s="2" t="n">
-        <v>325</v>
+        <v>268</v>
       </c>
       <c r="G273" s="2" t="n"/>
     </row>
@@ -39821,24 +39821,24 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>רבי מאיר בן שמעון המעילי</t>
+          <t>החיד״א (רבי חיים יוסף דוד אזולאי)</t>
         </is>
       </c>
       <c r="C274" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/2LqX1m0yUTIjrytoK1ZOD1</t>
+          <t>https://open.spotify.com/episode/2MiUUx51sCblnVdS9i61Xq</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>📜 רבי מאיר בן שמעון המעילי באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/393?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 החיד״א (רבי חיים יוסף דוד אזולאי) באוצר חכמים — המחקר המלא ורבותיו: https://ozar-chachamim-app.vercel.app/he/sage/325?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E274" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F274" s="2" t="n">
-        <v>393</v>
+        <v>325</v>
       </c>
       <c r="G274" s="2" t="n"/>
     </row>
@@ -39848,24 +39848,24 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>שרה אמנו</t>
+          <t>רבי מאיר בן שמעון המעילי</t>
         </is>
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/episode/2XYXmPscJIo8gLmJov6AFc</t>
+          <t>https://open.spotify.com/episode/2LqX1m0yUTIjrytoK1ZOD1</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>📜 שרה אמנו באוצר חכמים — המחקר המלא: https://ozar-chachamim-app.vercel.app/he/sage/448?utm_source=spotify&amp;utm_medium=podcast</t>
+          <t>📜 רבי מאיר בן שמעון המעילי באוצר חכמים — המחקר המלא ורבותיו ותלמידיו: https://ozar-chachamim-app.vercel.app/he/sage/393?utm_source=spotify&amp;utm_medium=podcast</t>
         </is>
       </c>
       <c r="E275" s="3" t="n">
         <v>30</v>
       </c>
       <c r="F275" s="2" t="n">
-        <v>448</v>
+        <v>393</v>
       </c>
       <c r="G275" s="2" t="n"/>
     </row>
@@ -44047,7 +44047,7 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>נתוני הצפיות נלקחו מ־YouTube ב־2026-10-24.</t>
+          <t>נתוני הצפיות נלקחו מ־YouTube ב־2026-10-25.</t>
         </is>
       </c>
     </row>
